--- a/resultado_consulta_entradas.xlsx
+++ b/resultado_consulta_entradas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G297"/>
+  <dimension ref="A1:G266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
         <v>2026</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1165.88</v>
+        <v>5807.05</v>
       </c>
     </row>
     <row r="3">
@@ -487,7 +487,7 @@
         <v>2026</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
         <v>4</v>
@@ -508,7 +508,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1380</v>
+        <v>686066.62</v>
       </c>
     </row>
     <row r="4">
@@ -516,7 +516,7 @@
         <v>2026</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>380</v>
+        <v>376632.69</v>
       </c>
     </row>
     <row r="5">
@@ -545,7 +545,7 @@
         <v>2026</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>810.5</v>
+        <v>8681.5</v>
       </c>
     </row>
     <row r="6">
@@ -574,10 +574,10 @@
         <v>2026</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -586,16 +586,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13266570000170</t>
+          <t>32801577000199</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MEDANGIO METROPOLITANA DO AGRESTE LTDA E</t>
+          <t>S. S. LOPES BARBOSA LTDA</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>9147.790000000001</v>
+        <v>4338.11</v>
       </c>
     </row>
     <row r="7">
@@ -603,10 +603,10 @@
         <v>2026</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -615,16 +615,16 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>43067449000180</t>
+          <t>13266570000170</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>DOCTORS ODONTOLOGIA ESPECIALIZADA LTDA</t>
+          <t>MEDANGIO METROPOLITANA DO AGRESTE LTDA E</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3977.46</v>
+        <v>7670.15</v>
       </c>
     </row>
     <row r="8">
@@ -632,28 +632,28 @@
         <v>2026</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SAO SEBASTIAO</t>
+          <t>ARAPIRACA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12481529000153</t>
+          <t>43067449000180</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FARMACIA SANTA QUITERIA LTDA</t>
+          <t>DOCTORS ODONTOLOGIA ESPECIALIZADA LTDA</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>165454.02</v>
+        <v>3559.03</v>
       </c>
     </row>
     <row r="9">
@@ -661,7 +661,7 @@
         <v>2026</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>119094.8</v>
+        <v>180206.35</v>
       </c>
     </row>
     <row r="10">
@@ -690,28 +690,28 @@
         <v>2026</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NEOPOLIS</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>19832324000114</t>
+          <t>24074229000139</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ND EVOLUTION LTDA</t>
+          <t>MURICI &amp; BRITO COMÉRCIO ATACADISTA LTDA</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>31390.65</v>
+        <v>1554345.88</v>
       </c>
     </row>
     <row r="11">
@@ -719,28 +719,28 @@
         <v>2026</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>IGREJA NOVA</t>
+          <t>ARAPIRACA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>21983447000106</t>
+          <t>06266166000130</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DROGATOP COMERCIO DE MEDICAMENTOS LTDA</t>
+          <t>E DE OLIVEIRA COSTA E CIA LTDA</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>74633.67999999999</v>
+        <v>97424.32000000001</v>
       </c>
     </row>
     <row r="12">
@@ -748,28 +748,28 @@
         <v>2026</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MACEIO</t>
+          <t>PALMEIRA DOS INDIOS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>35741347000170</t>
+          <t>32621975000123</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>D &amp; R MATERIAIS DE CONSTRUCAO LTDA</t>
+          <t>S V S DE AQUINO E CIA LTDA</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>14314.24</v>
+        <v>935143.0699999999</v>
       </c>
     </row>
     <row r="13">
@@ -777,28 +777,28 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MACEIO</t>
+          <t>SAO SEBASTIAO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>24074229000139</t>
+          <t>18990675000190</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MURICI &amp; BRITO COMÉRCIO ATACADISTA LTDA</t>
+          <t>AUTO POSTO ALVES DA SILVA LTDA</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1961106.09</v>
+        <v>370577.5</v>
       </c>
     </row>
     <row r="14">
@@ -806,28 +806,28 @@
         <v>2026</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ARAPIRACA</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>06266166000130</t>
+          <t>39514162000183</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>E DE OLIVEIRA COSTA E CIA LTDA</t>
+          <t>R. MATOS GESTAO EMPRESARIAL LTDA</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>203520.23</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="15">
@@ -835,28 +835,28 @@
         <v>2026</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ARAPIRACA</t>
+          <t>PENEDO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>09331370000186</t>
+          <t>03413023000116</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SEMEAR AGROPECUARIA LTDA</t>
+          <t>PENEDO TECIDOS LTDA</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>32165.33</v>
+        <v>93598.52</v>
       </c>
     </row>
     <row r="16">
@@ -864,24 +864,28 @@
         <v>2026</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ARAPIRACA</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21983447000289</t>
+          <t>03418947000105</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>DROGATOP COMERCIO DE MEDICAMENTOS LTDA</t>
+          <t>E F BOMFIM LTDA</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>40410.4</v>
+        <v>44175.03</v>
       </c>
     </row>
     <row r="17">
@@ -889,28 +893,28 @@
         <v>2026</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PALMEIRA DOS INDIOS</t>
+          <t>PENEDO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>32621975000123</t>
+          <t>27049257000194</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S V S DE AQUINO E CIA LTDA</t>
+          <t>A DE CASTRO DANIEL SERVIÇOS EIRELI</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1532590.81</v>
+        <v>172.31</v>
       </c>
     </row>
     <row r="18">
@@ -918,28 +922,28 @@
         <v>2026</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SAO SEBASTIAO</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>18990675000190</t>
+          <t>07724513000194</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AUTO POSTO ALVES DA SILVA LTDA</t>
+          <t>R. DE FARIAS LINS LTDA</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>344041.76</v>
+        <v>595884.55</v>
       </c>
     </row>
     <row r="19">
@@ -947,28 +951,24 @@
         <v>2026</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>45</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>MACEIO</t>
-        </is>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>39514162000183</t>
+          <t>32621975000204</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R. MATOS GESTAO EMPRESARIAL LTDA</t>
+          <t>S V S DE AQUINO E CIA LTDA</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1727.6</v>
+        <v>118719.51</v>
       </c>
     </row>
     <row r="20">
@@ -976,28 +976,28 @@
         <v>2026</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CRAIBAS</t>
+          <t>PILAR</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>36992498000163</t>
+          <t>34073492000167</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UNIPRECO ALIMENTOS EIRELI</t>
+          <t>GEOVANNE GOMES DOS SANTOS LTDA</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>32108.36</v>
+        <v>80245.48</v>
       </c>
     </row>
     <row r="21">
@@ -1005,28 +1005,28 @@
         <v>2026</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PENEDO</t>
+          <t>ARACAJU</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>03413023000116</t>
+          <t>05794150000138</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PENEDO TECIDOS LTDA</t>
+          <t>AMANDA SIQUEIRA DE LIMA DANTAS LTDA</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>41874.26</v>
+        <v>551238.29</v>
       </c>
     </row>
     <row r="22">
@@ -1034,28 +1034,24 @@
         <v>2026</v>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>49</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>ARAPIRACA</t>
-        </is>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>03418947000105</t>
+          <t>07724513000275</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>E F BOMFIM LTDA</t>
+          <t>R. DE FARIAS LINS LTDA</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>84082.56</v>
+        <v>543995.25</v>
       </c>
     </row>
     <row r="23">
@@ -1063,28 +1059,24 @@
         <v>2026</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>53</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>MACEIO</t>
-        </is>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>07724513000194</t>
+          <t>32860231000595</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>R. DE FARIAS LINS LTDA</t>
+          <t>KI BARATO - SM NEÓPOLIS</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>662125.26</v>
+        <v>2202457.74</v>
       </c>
     </row>
     <row r="24">
@@ -1092,24 +1084,24 @@
         <v>2026</v>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>32621975000204</t>
+          <t>32860231000676</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>S V S DE AQUINO E CIA LTDA</t>
+          <t>KI BARATO LTDA</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>744.04</v>
+        <v>866651.97</v>
       </c>
     </row>
     <row r="25">
@@ -1117,28 +1109,24 @@
         <v>2026</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>55</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>PILAR</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>34073492000167</t>
+          <t>32860231000838</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>GEOVANNE GOMES DOS SANTOS LTDA</t>
+          <t>KI BARATO LTDA</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>140006.65</v>
+        <v>5284006.78</v>
       </c>
     </row>
     <row r="26">
@@ -1146,28 +1134,24 @@
         <v>2026</v>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>56</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>ARACAJU</t>
-        </is>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>05794150000138</t>
+          <t>32860231000919</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AMANDA SIQUEIRA DE LIMA DANTAS LTDA</t>
+          <t>KI BARATO LTDA</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>762565.8199999999</v>
+        <v>1288650.25</v>
       </c>
     </row>
     <row r="27">
@@ -1175,24 +1159,28 @@
         <v>2026</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>57</v>
-      </c>
-      <c r="D27" t="inlineStr"/>
+        <v>64</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NOSSA SENHORA DE LOURDES</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>07724513000275</t>
+          <t>11939481000111</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>R. DE FARIAS LINS LTDA</t>
+          <t>TELES &amp; RESENDE COMERCIO LTDA</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>670030.74</v>
+        <v>298563.32</v>
       </c>
     </row>
     <row r="28">
@@ -1200,24 +1188,28 @@
         <v>2026</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>58</v>
-      </c>
-      <c r="D28" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>JAPOATA</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>32860231000595</t>
+          <t>41399647000115</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KI BARATO - SM NEÓPOLIS</t>
+          <t>GS COMERCIAL LTDA</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1848775.56</v>
+        <v>1827509.97</v>
       </c>
     </row>
     <row r="29">
@@ -1225,24 +1217,28 @@
         <v>2026</v>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>59</v>
-      </c>
-      <c r="D29" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PENEDO</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>32860231000676</t>
+          <t>41190987000131</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KI BARATO LTDA</t>
+          <t>LUCAS EMANUEL RESENDE CRUZ EIRELI</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1003970.66</v>
+        <v>109908.61</v>
       </c>
     </row>
     <row r="30">
@@ -1250,24 +1246,28 @@
         <v>2026</v>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>61</v>
-      </c>
-      <c r="D30" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ARAPIRACA</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>32860231000838</t>
+          <t>40578807000120</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>KI BARATO LTDA</t>
+          <t>ANALISE ADMINISTRADORA EMPRESARIAL LTDA</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>5145363.9</v>
+        <v>303.37</v>
       </c>
     </row>
     <row r="31">
@@ -1275,15 +1275,15 @@
         <v>2026</v>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>32860231000919</t>
+          <t>32860231001133</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1382592.31</v>
+        <v>2677929.86</v>
       </c>
     </row>
     <row r="32">
@@ -1300,28 +1300,28 @@
         <v>2026</v>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NOSSA SENHORA DE LOURDES</t>
+          <t>ARACAJU</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>11939481000111</t>
+          <t>33706943000193</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TELES &amp; RESENDE COMERCIO LTDA</t>
+          <t>ANALISE ASSESSORIA CONTABIL ARACAJU LTDA</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>290622.55</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="33">
@@ -1329,28 +1329,24 @@
         <v>2026</v>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>65</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>JAPOATA</t>
-        </is>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>41399647000115</t>
+          <t>32860231001214</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>GS COMERCIAL LTDA</t>
+          <t>KI BARATO LTDA</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1678955.52</v>
+        <v>89373.14999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1358,28 +1354,28 @@
         <v>2026</v>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>PENEDO</t>
+          <t>ARAPIRACA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>41190987000131</t>
+          <t>33160549000100</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>LUCAS EMANUEL RESENDE CRUZ EIRELI</t>
+          <t>ANALISE GESTÃO EMPRESARIAL LTDA</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>44097.68</v>
+        <v>949</v>
       </c>
     </row>
     <row r="35">
@@ -1387,28 +1383,28 @@
         <v>2026</v>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ARAPIRACA</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>40578807000120</t>
+          <t>20654295000127</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ANALISE ADMINISTRADORA EMPRESARIAL LTDA</t>
+          <t>V L Y COMERCIO E REPRESENTACOES COMERCIA</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>303.37</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="36">
@@ -1416,28 +1412,28 @@
         <v>2026</v>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ARAPIRACA</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>08763404000149</t>
+          <t>21186468000192</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>NEUZETE DOMINGOS SILVA PINHEIRO LTDA</t>
+          <t xml:space="preserve">LYRA E MONTEIRO COMERCIO DE EMBARCACOES </t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>360543.94</v>
+        <v>2186924.81</v>
       </c>
     </row>
     <row r="37">
@@ -1445,15 +1441,19 @@
         <v>2026</v>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" t="n">
-        <v>70</v>
-      </c>
-      <c r="D37" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NEOPOLIS</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>32860231001133</t>
+          <t>32860231000161</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1462,7 +1462,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2870064.5</v>
+        <v>175996.2</v>
       </c>
     </row>
     <row r="38">
@@ -1470,28 +1470,24 @@
         <v>2026</v>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>71</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>ARACAJU</t>
-        </is>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>33706943000193</t>
+          <t>32860231001567</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ANALISE ASSESSORIA CONTABIL ARACAJU LTDA</t>
+          <t>KI BARATO LTDA</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>3386</v>
+        <v>1457194.07</v>
       </c>
     </row>
     <row r="39">
@@ -1499,15 +1495,19 @@
         <v>2026</v>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>73</v>
-      </c>
-      <c r="D39" t="inlineStr"/>
+        <v>88</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>PROPRIA</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>32860231001214</t>
+          <t>32860231000757</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>41607.52</v>
+        <v>3725114.04</v>
       </c>
     </row>
     <row r="40">
@@ -1524,28 +1524,24 @@
         <v>2026</v>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>74</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>ARAPIRACA</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>33160549000100</t>
+          <t>05794150000219</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ANALISE GESTÃO EMPRESARIAL LTDA</t>
+          <t>AMANDA SIQUEIRA DE LIMA DANTAS LTDA</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>415.48</v>
+        <v>168099.05</v>
       </c>
     </row>
     <row r="41">
@@ -1553,28 +1549,24 @@
         <v>2026</v>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>83</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>DELMIRO GOUVEIA</t>
-        </is>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>19630593000106</t>
+          <t>05794150000308</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MARCONDE DE SOUZA GOMES</t>
+          <t>AMANDA SIQUEIRA DE LIMA DANTAS LTDA</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>232280.38</v>
+        <v>188249.95</v>
       </c>
     </row>
     <row r="42">
@@ -1582,28 +1574,24 @@
         <v>2026</v>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>84</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>MACEIO</t>
-        </is>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>21186468000192</t>
+          <t>05794150000480</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">LYRA E MONTEIRO COMERCIO DE EMBARCACOES </t>
+          <t>AMANDA SIQUEIRA DE LIMA DANTAS LTDA</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>5808728.91</v>
+        <v>173484.02</v>
       </c>
     </row>
     <row r="43">
@@ -1611,28 +1599,28 @@
         <v>2026</v>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NEOPOLIS</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>32860231000161</t>
+          <t>09231306000123</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>KI BARATO LTDA</t>
+          <t>CAVALCANTE &amp; LEITE LTDA</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>128419.54</v>
+        <v>1890721.46</v>
       </c>
     </row>
     <row r="44">
@@ -1640,24 +1628,24 @@
         <v>2026</v>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" t="n">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>32860231001567</t>
+          <t>29169293000117</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>KI BARATO LTDA</t>
+          <t>D R SOARES COWORKING</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1403303.21</v>
+        <v>484.02</v>
       </c>
     </row>
     <row r="45">
@@ -1665,28 +1653,24 @@
         <v>2026</v>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>88</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>PROPRIA</t>
-        </is>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>32860231000757</t>
+          <t>49648898000106</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KI BARATO LTDA</t>
+          <t>VIDRACARIA UNIAO LTDA</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>4361255.64</v>
+        <v>38953.3</v>
       </c>
     </row>
     <row r="46">
@@ -1694,24 +1678,24 @@
         <v>2026</v>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>09331370000267</t>
+          <t>42200370000112</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SEMEAR AGROPECUARIA LTDA</t>
+          <t>MURO ALTO COMERCIO E SERVICOS DE ALIMENT</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>139795</v>
+        <v>223018.22</v>
       </c>
     </row>
     <row r="47">
@@ -1719,24 +1703,24 @@
         <v>2026</v>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>05794150000219</t>
+          <t>50687208000107</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AMANDA SIQUEIRA DE LIMA DANTAS LTDA</t>
+          <t>NETOS SORVETERIA LTDA</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>182388.22</v>
+        <v>2703.2</v>
       </c>
     </row>
     <row r="48">
@@ -1744,24 +1728,24 @@
         <v>2026</v>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>05794150000308</t>
+          <t>11449511000373</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AMANDA SIQUEIRA DE LIMA DANTAS LTDA</t>
+          <t>ACO BOMPRECO COMERCIAL LTDA</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>199616.72</v>
+        <v>400556.91</v>
       </c>
     </row>
     <row r="49">
@@ -1769,15 +1753,15 @@
         <v>2026</v>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>05794150000480</t>
+          <t>05794150000561</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1786,7 +1770,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>201823.6</v>
+        <v>165633.37</v>
       </c>
     </row>
     <row r="50">
@@ -1794,28 +1778,24 @@
         <v>2026</v>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>95</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>MACEIO</t>
-        </is>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>09231306000123</t>
+          <t>50141499000125</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CAVALCANTE &amp; LEITE LTDA</t>
+          <t>TATIANE DO AMARAL SILVA LTDA</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2710666.83</v>
+        <v>5777.63</v>
       </c>
     </row>
     <row r="51">
@@ -1823,24 +1803,24 @@
         <v>2026</v>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>29169293000117</t>
+          <t>19971010000100</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>D R SOARES COWORKING</t>
+          <t>J R A CONSTRUTORA LTDA</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1.73</v>
+        <v>48544.34</v>
       </c>
     </row>
     <row r="52">
@@ -1848,24 +1828,24 @@
         <v>2026</v>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C52" t="n">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>49648898000106</t>
+          <t>26021699000240</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>VIDRACARIA UNIAO LTDA</t>
+          <t>L. C. DOS SANTOS JUNIOR E CIA LTDA</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>46758.18</v>
+        <v>66158.8</v>
       </c>
     </row>
     <row r="53">
@@ -1873,24 +1853,28 @@
         <v>2026</v>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53" t="n">
-        <v>110</v>
-      </c>
-      <c r="D53" t="inlineStr"/>
+        <v>144</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AQUIDABA</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>42200370000112</t>
+          <t>04731902000159</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MURO ALTO COMERCIO E SERVICOS DE ALIMENT</t>
+          <t>MATERIAL DE CONSTRUCAO PRONTA ENTREGA LT</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>293592.15</v>
+        <v>142963.63</v>
       </c>
     </row>
     <row r="54">
@@ -1898,24 +1882,28 @@
         <v>2026</v>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>119</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
+        <v>145</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AQUIDABA</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>50687208000107</t>
+          <t>02466007000129</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>NETOS SORVETERIA LTDA</t>
+          <t>SUPERMERCADO 2000 LTDA</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>5322</v>
+        <v>1441722.01</v>
       </c>
     </row>
     <row r="55">
@@ -1923,24 +1911,28 @@
         <v>2026</v>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55" t="n">
-        <v>128</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
+        <v>149</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NOSSA SENHORA DA GLORIA</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>11449511000373</t>
+          <t>43506193000160</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ACO BOMPRECO COMERCIAL LTDA</t>
+          <t>KI DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>259050.69</v>
+        <v>3190758.39</v>
       </c>
     </row>
     <row r="56">
@@ -1948,24 +1940,28 @@
         <v>2026</v>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" t="n">
-        <v>131</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
+        <v>154</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NEOPOLIS</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>05794150000561</t>
+          <t>13111703000139</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AMANDA SIQUEIRA DE LIMA DANTAS LTDA</t>
+          <t xml:space="preserve">MARAVILHA LANCHONETE E PANIFICACAO LTDA </t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>198270.31</v>
+        <v>65541.98</v>
       </c>
     </row>
     <row r="57">
@@ -1973,24 +1969,28 @@
         <v>2026</v>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57" t="n">
-        <v>134</v>
-      </c>
-      <c r="D57" t="inlineStr"/>
+        <v>159</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>PETROLANDIA</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>07749075000119</t>
+          <t>18614955000102</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARITIME SHIP SERVICE LTDA </t>
+          <t>PISEBEM COMERCIO DE REVESTIMENTO LTDA</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>12204.12</v>
+        <v>374773.08</v>
       </c>
     </row>
     <row r="58">
@@ -1998,24 +1998,28 @@
         <v>2026</v>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C58" t="n">
-        <v>135</v>
-      </c>
-      <c r="D58" t="inlineStr"/>
+        <v>160</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>MATA GRANDE</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>50141499000125</t>
+          <t>04842228000180</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>TATIANE DO AMARAL SILVA LTDA</t>
+          <t>SUPERMERCADO BRAGANCA LTDA</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>37486.03</v>
+        <v>403545.31</v>
       </c>
     </row>
     <row r="59">
@@ -2023,24 +2027,28 @@
         <v>2026</v>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59" t="n">
-        <v>136</v>
-      </c>
-      <c r="D59" t="inlineStr"/>
+        <v>161</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>DELMIRO GOUVEIA</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>19971010000100</t>
+          <t>14123179000189</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>J R A CONSTRUTORA LTDA</t>
+          <t>T&amp;S INFORMATICA LTDA - ME</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>36852.09</v>
+        <v>34266.99</v>
       </c>
     </row>
     <row r="60">
@@ -2048,24 +2056,28 @@
         <v>2026</v>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60" t="n">
-        <v>137</v>
-      </c>
-      <c r="D60" t="inlineStr"/>
+        <v>162</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>MATA GRANDE</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>26021699000240</t>
+          <t>21232450000180</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>L. C. DOS SANTOS JUNIOR E CIA LTDA</t>
+          <t>NELSON MANOEL DA SILVA - ME</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>68731.62</v>
+        <v>18891.07</v>
       </c>
     </row>
     <row r="61">
@@ -2073,28 +2085,28 @@
         <v>2026</v>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61" t="n">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>AQUIDABA</t>
+          <t>MATA GRANDE</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>15714150000134</t>
+          <t>10931715000111</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RESTAURANTE 2000 LTDA</t>
+          <t>NIVALDA MARIA VILARINDO DA SILVA - ME</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>11232.26</v>
+        <v>171016.59</v>
       </c>
     </row>
     <row r="62">
@@ -2102,28 +2114,28 @@
         <v>2026</v>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62" t="n">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>AQUIDABA</t>
+          <t>MATA GRANDE</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>29762970000106</t>
+          <t>12317881000158</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>FELIPE MADEIREIRA E MATERIAL DE CONSTRUC</t>
+          <t>JOSE FAGNER FERREIRA DA SILVA E CIA LTDA</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>161456.56</v>
+        <v>689729.1800000001</v>
       </c>
     </row>
     <row r="63">
@@ -2131,28 +2143,28 @@
         <v>2026</v>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C63" t="n">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>AQUIDABA</t>
+          <t>INHAPI</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>04731902000159</t>
+          <t>29040567000173</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MATERIAL DE CONSTRUCAO PRONTA ENTREGA LT</t>
+          <t>ALFREDO VIEIRA DO NASCIMENTO GUERRA - ME</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>145333.52</v>
+        <v>327.91</v>
       </c>
     </row>
     <row r="64">
@@ -2160,28 +2172,28 @@
         <v>2026</v>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64" t="n">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>AQUIDABA</t>
+          <t>MATA GRANDE</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>02466007000129</t>
+          <t>34550065000122</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SUPERMERCADO 2000 LTDA</t>
+          <t>ALDEMIR DE LIMA FREITAS CONSTRUCAO</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1763544.69</v>
+        <v>40778.3</v>
       </c>
     </row>
     <row r="65">
@@ -2189,28 +2201,28 @@
         <v>2026</v>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65" t="n">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NOSSA SENHORA DA GLORIA</t>
+          <t>PAULO AFONSO</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>43506193000160</t>
+          <t>10892281000198</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>KI DISTRIBUIDORA LTDA</t>
+          <t>GOMES GOUVEIA RETIFICA LTDA</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>2838732.87</v>
+        <v>77434.58</v>
       </c>
     </row>
     <row r="66">
@@ -2218,28 +2230,28 @@
         <v>2026</v>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66" t="n">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NEOPOLIS</t>
+          <t>DELMIRO GOUVEIA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>13111703000139</t>
+          <t>17855713000130</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARAVILHA LANCHONETE E PANIFICACAO LTDA </t>
+          <t>AMARAL E BENE LTDA</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>30622.1</v>
+        <v>86898.60000000001</v>
       </c>
     </row>
     <row r="67">
@@ -2247,28 +2259,28 @@
         <v>2026</v>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C67" t="n">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>PETROLANDIA</t>
+          <t>PAULO AFONSO</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>18614955000102</t>
+          <t>01807929000190</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>PISEBEM COMERCIO DE REVESTIMENTO LTDA</t>
+          <t>RANIERE LEANDRO DE MORAIS</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>276041.96</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="68">
@@ -2276,28 +2288,28 @@
         <v>2026</v>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C68" t="n">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>MATA GRANDE</t>
+          <t>PAULO AFONSO</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>04842228000180</t>
+          <t>23320287000132</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SUPERMERCADO BRAGANCA LTDA</t>
+          <t>RAIAN LEANDRO DE MORAIS</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>700603.6899999999</v>
+        <v>519106.49</v>
       </c>
     </row>
     <row r="69">
@@ -2305,28 +2317,28 @@
         <v>2026</v>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69" t="n">
-        <v>161</v>
+        <v>206</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DELMIRO GOUVEIA</t>
+          <t>ARAPIRACA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>14123179000189</t>
+          <t>12198552000135</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>T&amp;S INFORMATICA LTDA - ME</t>
+          <t>DEPOSITO DE MADEIRAS AMAZONIA EIRELI - E</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>168607.07</v>
+        <v>140346.15</v>
       </c>
     </row>
     <row r="70">
@@ -2334,28 +2346,28 @@
         <v>2026</v>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70" t="n">
-        <v>162</v>
+        <v>207</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>MATA GRANDE</t>
+          <t>ARAPIRACA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>21232450000180</t>
+          <t>10812956000141</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>NELSON MANOEL DA SILVA - ME</t>
+          <t>AMAZONPLAC COMERCIO DE MADEIRAS LTDA EPP</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>21340.85</v>
+        <v>93587.71000000001</v>
       </c>
     </row>
     <row r="71">
@@ -2363,28 +2375,28 @@
         <v>2026</v>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71" t="n">
-        <v>163</v>
+        <v>213</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>MATA GRANDE</t>
+          <t>ARAPIRACA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>10931715000111</t>
+          <t>12133261000169</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>NIVALDA MARIA VILARINDO DA SILVA - ME</t>
+          <t>INDUSTRIA DE MOVEIS DO AGRESTE LTDA</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>247617.38</v>
+        <v>24884</v>
       </c>
     </row>
     <row r="72">
@@ -2392,28 +2404,28 @@
         <v>2026</v>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72" t="n">
-        <v>166</v>
+        <v>215</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>MATA GRANDE</t>
+          <t>ARAPIRACA</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>18151612000140</t>
+          <t>12639726000158</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CASSIO EWERTON ALVES LACERDA</t>
+          <t>H T DA SILVA MALAQUIAS CONSTRUÇÕES - ME</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1867.18</v>
+        <v>30525.46</v>
       </c>
     </row>
     <row r="73">
@@ -2421,28 +2433,28 @@
         <v>2026</v>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>167</v>
+        <v>216</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>MATA GRANDE</t>
+          <t>ARAPIRACA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>12317881000158</t>
+          <t>12651098000126</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>JOSE FAGNER FERREIRA DA SILVA E CIA LTDA</t>
+          <t>INDUSTRIA ALAGOANA DE PORTAS LTDA</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>750624.1899999999</v>
+        <v>34090.4</v>
       </c>
     </row>
     <row r="74">
@@ -2450,28 +2462,28 @@
         <v>2026</v>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C74" t="n">
-        <v>178</v>
+        <v>218</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>MATA GRANDE</t>
+          <t>ARAPIRACA</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>34550065000122</t>
+          <t>14726039000103</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>ALDEMIR DE LIMA FREITAS CONSTRUCAO</t>
+          <t>VISÃO PROPAGANDA E PUBLICIDADE LTDA</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>40722.85</v>
+        <v>1396.28</v>
       </c>
     </row>
     <row r="75">
@@ -2479,28 +2491,28 @@
         <v>2026</v>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C75" t="n">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>PAULO AFONSO</t>
+          <t>ARAPIRACA</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>10892281000198</t>
+          <t>07246670000131</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>GOMES GOUVEIA RETIFICA LTDA</t>
+          <t>S. C. DO CARMO CONFECCOES</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>132672.07</v>
+        <v>91018.23</v>
       </c>
     </row>
     <row r="76">
@@ -2508,28 +2520,28 @@
         <v>2026</v>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76" t="n">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>INHAPI</t>
+          <t>ARAPIRACA</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>07205130000100</t>
+          <t>16912703000126</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>JS SUPERMERCADO LTDA</t>
+          <t>AÇO LIDER LTDA</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>561937.72</v>
+        <v>1156306.49</v>
       </c>
     </row>
     <row r="77">
@@ -2537,28 +2549,28 @@
         <v>2026</v>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C77" t="n">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>DELMIRO GOUVEIA</t>
+          <t>ARAPIRACA</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>17855713000130</t>
+          <t>17967085000184</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>AMARAL E BENE LTDA</t>
+          <t>AGRESTE COMERCIO DE AUTOMOVEIS EIRELI</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>180087.76</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="78">
@@ -2566,28 +2578,28 @@
         <v>2026</v>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78" t="n">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>PAULO AFONSO</t>
+          <t>PALMEIRA DOS INDIOS</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>01807929000190</t>
+          <t>10657384000173</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RANIERE LEANDRO DE MORAIS</t>
+          <t>BEDA TRATORES LTDA</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>2000</v>
+        <v>28850</v>
       </c>
     </row>
     <row r="79">
@@ -2595,28 +2607,28 @@
         <v>2026</v>
       </c>
       <c r="B79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" t="n">
-        <v>192</v>
+        <v>235</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>PAULO AFONSO</t>
+          <t>MAJOR ISIDORO</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>23320287000132</t>
+          <t>01403884000198</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RAIAN LEANDRO DE MORAIS</t>
+          <t>VALDEMOR ARAUJO DA SILVA LTDA</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>739452.63</v>
+        <v>260734.11</v>
       </c>
     </row>
     <row r="80">
@@ -2624,28 +2636,28 @@
         <v>2026</v>
       </c>
       <c r="B80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80" t="n">
-        <v>196</v>
+        <v>236</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SAO JOSE DA TAPERA</t>
+          <t>MAJOR ISIDORO</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>46493152000174</t>
+          <t>07889772000175</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CBMT- COMPANHIA DE BEBIDAS MIRANDA TAPER</t>
+          <t>E. T. B. ARAUJO LTDA</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>79243.25</v>
       </c>
     </row>
     <row r="81">
@@ -2653,10 +2665,10 @@
         <v>2026</v>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" t="n">
-        <v>206</v>
+        <v>246</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2665,16 +2677,16 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>12198552000135</t>
+          <t>24850747000105</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>DEPOSITO DE MADEIRAS AMAZONIA EIRELI - E</t>
+          <t>BRASLIMP DISTRIBUIDORA LTDA-ME</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>155844.62</v>
+        <v>7745.48</v>
       </c>
     </row>
     <row r="82">
@@ -2682,10 +2694,10 @@
         <v>2026</v>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82" t="n">
-        <v>207</v>
+        <v>247</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -2694,16 +2706,16 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>10812956000141</t>
+          <t>00278252000187</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AMAZONPLAC COMERCIO DE MADEIRAS LTDA EPP</t>
+          <t>SERVIBRAS COMERCIO E SERVICOS TECNICOS L</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>7993.34</v>
+        <v>41808.75</v>
       </c>
     </row>
     <row r="83">
@@ -2711,10 +2723,10 @@
         <v>2026</v>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83" t="n">
-        <v>213</v>
+        <v>250</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -2723,16 +2735,16 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>12133261000169</t>
+          <t>35635333000171</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>INDUSTRIA DE MOVEIS DO AGRESTE LTDA</t>
+          <t>EDIAL EMPRESA DIVULGADORA ARAPIRACA LTDA</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>11047.8</v>
+        <v>30725.22</v>
       </c>
     </row>
     <row r="84">
@@ -2740,10 +2752,10 @@
         <v>2026</v>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84" t="n">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -2752,16 +2764,16 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>12639726000158</t>
+          <t>28004806000177</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>H T DA SILVA MALAQUIAS CONSTRUÇÕES - ME</t>
+          <t>CARDAN ARAPIRACA COMERCIO DE PECAS E SER</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>30051.38</v>
+        <v>34917.26</v>
       </c>
     </row>
     <row r="85">
@@ -2769,10 +2781,10 @@
         <v>2026</v>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85" t="n">
-        <v>216</v>
+        <v>257</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -2781,16 +2793,16 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>12651098000126</t>
+          <t>29180665000106</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>INDUSTRIA ALAGOANA DE PORTAS LTDA</t>
+          <t>PEC GARDEN COMERCIO DE COSMETICOS EIRELI</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>10742.21</v>
+        <v>14423.47</v>
       </c>
     </row>
     <row r="86">
@@ -2798,28 +2810,28 @@
         <v>2026</v>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86" t="n">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ARAPIRACA</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>14726039000103</t>
+          <t>11449511000101</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>VISÃO PROPAGANDA E PUBLICIDADE LTDA</t>
+          <t>ACO BOMPRECO COMERCIAL LTDA</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>2502.39</v>
+        <v>769451.4300000001</v>
       </c>
     </row>
     <row r="87">
@@ -2827,28 +2839,28 @@
         <v>2026</v>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87" t="n">
-        <v>222</v>
+        <v>262</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ARAPIRACA</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>07246670000131</t>
+          <t>26058879000116</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>S. C. DO CARMO CONFECCOES</t>
+          <t>AB INDUSTRIA METALÚRGICA E COMERCIO EIRE</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>280888.25</v>
+        <v>365337.41</v>
       </c>
     </row>
     <row r="88">
@@ -2856,10 +2868,10 @@
         <v>2026</v>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88" t="n">
-        <v>223</v>
+        <v>263</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2868,16 +2880,16 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>16912703000126</t>
+          <t>18765937000113</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AÇO LIDER LTDA</t>
+          <t>ISAAC ANTONIO MOURA DA NOBREGA</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>993595.97</v>
+        <v>1480934.3</v>
       </c>
     </row>
     <row r="89">
@@ -2885,10 +2897,10 @@
         <v>2026</v>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89" t="n">
-        <v>226</v>
+        <v>267</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -2897,16 +2909,16 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>17967085000184</t>
+          <t>00808941000156</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AGRESTE COMERCIO DE AUTOMOVEIS EIRELI</t>
+          <t>ESCOLA DE EDUCACAO BASICA SANTA CLARA</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>125000</v>
+        <v>1643.18</v>
       </c>
     </row>
     <row r="90">
@@ -2914,28 +2926,28 @@
         <v>2026</v>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90" t="n">
-        <v>229</v>
+        <v>268</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>PALMEIRA DOS INDIOS</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>10657384000173</t>
+          <t>17926307000110</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>BEDA TRATORES LTDA</t>
+          <t>MESSIAS - SOCIEDADE INDIVIDUAL DE ADVOCA</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>203901.53</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="91">
@@ -2943,28 +2955,28 @@
         <v>2026</v>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C91" t="n">
-        <v>232</v>
+        <v>272</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>PALMEIRA DOS INDIOS</t>
+          <t>SAO SEBASTIAO</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>18835068000156</t>
+          <t>08983051000192</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>BEDA MAQUINAS AGRICOLAS EIRELI - ME</t>
+          <t>LEANDRO OLIVEIRA SILVA INFORMATICA</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>41824.98</v>
+        <v>18667.39</v>
       </c>
     </row>
     <row r="92">
@@ -2972,28 +2984,28 @@
         <v>2026</v>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C92" t="n">
-        <v>235</v>
+        <v>277</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>MAJOR ISIDORO</t>
+          <t>COITE DO NOIA</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>01403884000198</t>
+          <t>27947305000161</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>VALDEMOR ARAUJO DA SILVA LTDA</t>
+          <t>IURY WALYSSON DE AMORIM MELO EIRELI</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>724530.79</v>
+        <v>88723.22</v>
       </c>
     </row>
     <row r="93">
@@ -3001,28 +3013,28 @@
         <v>2026</v>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93" t="n">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>MAJOR ISIDORO</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>07889772000175</t>
+          <t>32964863000175</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>E. T. B. ARAUJO LTDA</t>
+          <t>PEC MACEIO COMERCIO DE COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>39703.46</v>
+        <v>28712.53</v>
       </c>
     </row>
     <row r="94">
@@ -3030,28 +3042,28 @@
         <v>2026</v>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C94" t="n">
-        <v>238</v>
+        <v>279</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ESTRELA DE ALAGOAS</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>20085483000181</t>
+          <t>32965077000192</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>J. J. AUGUSTINHO  - ME</t>
+          <t>PEC PATIO COMERCIO DE COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>184032.7</v>
+        <v>39022.15</v>
       </c>
     </row>
     <row r="95">
@@ -3059,10 +3071,10 @@
         <v>2026</v>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C95" t="n">
-        <v>246</v>
+        <v>283</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -3071,16 +3083,16 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>24850747000105</t>
+          <t>03571483000172</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>BRASLIMP DISTRIBUIDORA LTDA-ME</t>
+          <t>VIVA ATACAREJO EIRELI</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>28111.25</v>
+        <v>774624.66</v>
       </c>
     </row>
     <row r="96">
@@ -3088,28 +3100,28 @@
         <v>2026</v>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C96" t="n">
-        <v>247</v>
+        <v>286</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ARAPIRACA</t>
+          <t>GIRAU DO PONCIANO</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>00278252000187</t>
+          <t>33609812000198</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>SERVIBRAS COMERCIO E SERVICOS TECNICOS L</t>
+          <t>CAVALCANTE BEBIDAS LTDA</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>103634.17</v>
+        <v>27956.52</v>
       </c>
     </row>
     <row r="97">
@@ -3117,28 +3129,28 @@
         <v>2026</v>
       </c>
       <c r="B97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C97" t="n">
-        <v>250</v>
+        <v>293</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ARAPIRACA</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>35635333000171</t>
+          <t>12207619000150</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>EDIAL EMPRESA DIVULGADORA ARAPIRACA LTDA</t>
+          <t>RENATO CAVALCANTE LINS</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>930.29</v>
+        <v>314086.99</v>
       </c>
     </row>
     <row r="98">
@@ -3146,28 +3158,28 @@
         <v>2026</v>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98" t="n">
-        <v>253</v>
+        <v>294</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ARAPIRACA</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>28004806000177</t>
+          <t>26021699000160</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CARDAN ARAPIRACA COMERCIO DE PECAS E SER</t>
+          <t>L. C. DOS SANTOS JUNIOR E CIA LTDA</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>24929.76</v>
+        <v>2149898.87</v>
       </c>
     </row>
     <row r="99">
@@ -3175,10 +3187,10 @@
         <v>2026</v>
       </c>
       <c r="B99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C99" t="n">
-        <v>257</v>
+        <v>296</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -3187,16 +3199,16 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>29180665000106</t>
+          <t>24176992000170</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>PEC GARDEN COMERCIO DE COSMETICOS EIRELI</t>
+          <t>ASSOCIACAO DOS DEFICIENTES F E MENTAIS D</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>12494.05</v>
+        <v>105164.8</v>
       </c>
     </row>
     <row r="100">
@@ -3204,28 +3216,28 @@
         <v>2026</v>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C100" t="n">
-        <v>260</v>
+        <v>297</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>MACEIO</t>
+          <t>ARAPIRACA</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>11449511000101</t>
+          <t>15835897000140</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ACO BOMPRECO COMERCIAL LTDA</t>
+          <t>J.E. SANTOS DA SILVA</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>1345528.91</v>
+        <v>82208.03999999999</v>
       </c>
     </row>
     <row r="101">
@@ -3233,28 +3245,28 @@
         <v>2026</v>
       </c>
       <c r="B101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C101" t="n">
-        <v>262</v>
+        <v>306</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>MACEIO</t>
+          <t>ARAPIRACA</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>26058879000116</t>
+          <t>34834110000170</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>AB INDUSTRIA METALÚRGICA E COMERCIO EIRE</t>
+          <t>R. P. BROWNIE E BOLOS LTDA</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>710195.54</v>
+        <v>396</v>
       </c>
     </row>
     <row r="102">
@@ -3262,10 +3274,10 @@
         <v>2026</v>
       </c>
       <c r="B102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C102" t="n">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -3274,16 +3286,16 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>18765937000113</t>
+          <t>39852829000158</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>ISAAC ANTONIO MOURA DA NOBREGA</t>
+          <t>ARMAZEM SALUTE PRODUTOS NATURAIS LTDA</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>2344305.12</v>
+        <v>67691.47</v>
       </c>
     </row>
     <row r="103">
@@ -3291,28 +3303,28 @@
         <v>2026</v>
       </c>
       <c r="B103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C103" t="n">
-        <v>267</v>
+        <v>313</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ARAPIRACA</t>
+          <t>PENEDO</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>00808941000156</t>
+          <t>21640463000198</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ESCOLA DE EDUCACAO BASICA SANTA CLARA</t>
+          <t>ACLECIO EVANGELISTA PEREIRA EIRELI</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>543.01</v>
+        <v>92590.99000000001</v>
       </c>
     </row>
     <row r="104">
@@ -3320,10 +3332,10 @@
         <v>2026</v>
       </c>
       <c r="B104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C104" t="n">
-        <v>268</v>
+        <v>319</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -3332,16 +3344,16 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>17926307000110</t>
+          <t>41160020000107</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>MESSIAS - SOCIEDADE INDIVIDUAL DE ADVOCA</t>
+          <t>OLIVEIRA E OLIVEIRA LTDA</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>2118</v>
+        <v>903</v>
       </c>
     </row>
     <row r="105">
@@ -3349,28 +3361,28 @@
         <v>2026</v>
       </c>
       <c r="B105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C105" t="n">
-        <v>272</v>
+        <v>321</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>SAO SEBASTIAO</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>08983051000192</t>
+          <t>41916574000191</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>LEANDRO OLIVEIRA SILVA INFORMATICA</t>
+          <t>MGA AGENCIA DIGITAL LTDA</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>1538.24</v>
+        <v>2123.17</v>
       </c>
     </row>
     <row r="106">
@@ -3378,28 +3390,28 @@
         <v>2026</v>
       </c>
       <c r="B106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106" t="n">
-        <v>277</v>
+        <v>322</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>COITE DO NOIA</t>
+          <t>ARAPIRACA</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>27947305000161</t>
+          <t>41967862000175</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>IURY WALYSSON DE AMORIM MELO EIRELI</t>
+          <t>COSTA MELO SOLUCOES EMPRESARIAIS LTDA</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>158253.59</v>
+        <v>976.0599999999999</v>
       </c>
     </row>
     <row r="107">
@@ -3407,10 +3419,10 @@
         <v>2026</v>
       </c>
       <c r="B107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C107" t="n">
-        <v>278</v>
+        <v>326</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -3419,16 +3431,16 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>32964863000175</t>
+          <t>42642452000117</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>PEC MACEIO COMERCIO DE COSMETICOS LTDA</t>
+          <t>AURICHERLA DA G. BARROS COMERCIO DE ALIM</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>25279.79</v>
+        <v>675535.03</v>
       </c>
     </row>
     <row r="108">
@@ -3436,28 +3448,28 @@
         <v>2026</v>
       </c>
       <c r="B108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C108" t="n">
-        <v>279</v>
+        <v>328</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>MACEIO</t>
+          <t>PAULO AFONSO</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>32965077000192</t>
+          <t>43173916000156</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>PEC PATIO COMERCIO DE COSMETICOS LTDA</t>
+          <t>A. C. RODRIGUES MATOS SILVA</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>22688.56</v>
+        <v>55538.6</v>
       </c>
     </row>
     <row r="109">
@@ -3465,28 +3477,28 @@
         <v>2026</v>
       </c>
       <c r="B109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C109" t="n">
-        <v>283</v>
+        <v>331</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ARAPIRACA</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>03571483000172</t>
+          <t>16690055000100</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>VIVA ATACAREJO EIRELI</t>
+          <t>BOMBONIERE BRASIL DOCE LTDA</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1281175.17</v>
+        <v>338137.23</v>
       </c>
     </row>
     <row r="110">
@@ -3494,28 +3506,28 @@
         <v>2026</v>
       </c>
       <c r="B110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C110" t="n">
-        <v>286</v>
+        <v>334</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>GIRAU DO PONCIANO</t>
+          <t>ARACAJU</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>33609812000198</t>
+          <t>13161435000160</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CAVALCANTE BEBIDAS LTDA</t>
+          <t>AGROVEL AGRICULTURA E VETERINÁRIA LTDA</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>34928.93</v>
+        <v>91406.21000000001</v>
       </c>
     </row>
     <row r="111">
@@ -3523,28 +3535,28 @@
         <v>2026</v>
       </c>
       <c r="B111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C111" t="n">
-        <v>287</v>
+        <v>336</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ARAPIRACA</t>
+          <t>ARACAJU</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>33609673000100</t>
+          <t>32853772000162</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>ENG ENERGIA SOLAR BRASIL LTDA</t>
+          <t>SERIGY BRICOLAGEM LTDA</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>162980.22</v>
+        <v>114492.03</v>
       </c>
     </row>
     <row r="112">
@@ -3552,28 +3564,28 @@
         <v>2026</v>
       </c>
       <c r="B112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C112" t="n">
-        <v>288</v>
+        <v>337</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>GARANHUNS</t>
+          <t>ARACAJU</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>33813279000181</t>
+          <t>32607758000189</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>ESTRUTURACO COMERCIAL DE FERRO LTDA</t>
+          <t>SERIGY SERVIÇOS EIRELI</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>68985.91</v>
+        <v>515.88</v>
       </c>
     </row>
     <row r="113">
@@ -3581,28 +3593,28 @@
         <v>2026</v>
       </c>
       <c r="B113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C113" t="n">
-        <v>293</v>
+        <v>339</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>MACEIO</t>
+          <t>MESSIAS</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>12207619000150</t>
+          <t>43946463000153</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>RENATO CAVALCANTE LINS</t>
+          <t>MAC ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>381862.79</v>
+        <v>574051.8</v>
       </c>
     </row>
     <row r="114">
@@ -3610,28 +3622,28 @@
         <v>2026</v>
       </c>
       <c r="B114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C114" t="n">
-        <v>294</v>
+        <v>341</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>MACEIO</t>
+          <t>SATUBA</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>26021699000160</t>
+          <t>11330714000184</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>L. C. DOS SANTOS JUNIOR E CIA LTDA</t>
+          <t>JOSE DA SILVA ALMEIDA</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>2862126.62</v>
+        <v>123767.24</v>
       </c>
     </row>
     <row r="115">
@@ -3639,28 +3651,28 @@
         <v>2026</v>
       </c>
       <c r="B115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C115" t="n">
-        <v>296</v>
+        <v>342</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ARAPIRACA</t>
+          <t>LAGARTO</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>24176992000170</t>
+          <t>16881386000128</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>ASSOCIACAO DOS DEFICIENTES F E MENTAIS D</t>
+          <t>ACO BOMPRECO COMERCIAL LAGARTO LTDA</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>66334</v>
+        <v>472889.13</v>
       </c>
     </row>
     <row r="116">
@@ -3668,28 +3680,28 @@
         <v>2026</v>
       </c>
       <c r="B116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C116" t="n">
-        <v>297</v>
+        <v>345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ARAPIRACA</t>
+          <t>ARACAJU</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>15835897000140</t>
+          <t>37539899000125</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>J.E. SANTOS DA SILVA</t>
+          <t>NUTRIAGRO COMERCIO DE MEDICAMENTOS VETER</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>206135.16</v>
+        <v>67389.06</v>
       </c>
     </row>
     <row r="117">
@@ -3697,28 +3709,28 @@
         <v>2026</v>
       </c>
       <c r="B117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C117" t="n">
-        <v>298</v>
+        <v>347</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>MACEIO</t>
+          <t>ARACAJU</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>10679721000123</t>
+          <t>20972935000147</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>LEITE &amp; PARANHOS LTDA</t>
+          <t>W. DANTAS PATRIMONIAL LTDA</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>20000</v>
+        <v>810.5</v>
       </c>
     </row>
     <row r="118">
@@ -3726,28 +3738,28 @@
         <v>2026</v>
       </c>
       <c r="B118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C118" t="n">
-        <v>300</v>
+        <v>348</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>BATALHA</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>33170658000109</t>
+          <t>44432729000102</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>MARIA GRAZIELE PEREIRA TIMOTEO AUTO PECA</t>
+          <t>COMERCIAL ATACADISTA DE ACO E FERRO LTDA</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>77183.78</v>
+        <v>318480.58</v>
       </c>
     </row>
     <row r="119">
@@ -3755,28 +3767,28 @@
         <v>2026</v>
       </c>
       <c r="B119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C119" t="n">
-        <v>306</v>
+        <v>353</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ARAPIRACA</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>34834110000170</t>
+          <t>26678956000130</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>R. P. BROWNIE E BOLOS LTDA</t>
+          <t>J R A PARAFUSOS MAQUINAS E FERRAMENTAS L</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>5379.36</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="120">
@@ -3784,28 +3796,28 @@
         <v>2026</v>
       </c>
       <c r="B120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C120" t="n">
-        <v>311</v>
+        <v>355</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ARAPIRACA</t>
+          <t>BOM CONSELHO</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>39852829000158</t>
+          <t>17370582000109</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>ARMAZEM SALUTE PRODUTOS NATURAIS LTDA</t>
+          <t>AGROVAN COMERCIO VAREJISTA DE AVES LTDA</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>66068.58</v>
+        <v>1793896.7</v>
       </c>
     </row>
     <row r="121">
@@ -3813,28 +3825,28 @@
         <v>2026</v>
       </c>
       <c r="B121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C121" t="n">
-        <v>313</v>
+        <v>356</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>PENEDO</t>
+          <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>21640463000198</t>
+          <t>03884414500371</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>ACLECIO EVANGELISTA PEREIRA EIRELI</t>
+          <t>CARLOS WALDEMAR DE ALMEIDA DANTAS</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>1872361.2</v>
+        <v>256650</v>
       </c>
     </row>
     <row r="122">
@@ -3842,28 +3854,28 @@
         <v>2026</v>
       </c>
       <c r="B122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C122" t="n">
-        <v>314</v>
+        <v>359</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>RIO LARGO</t>
+          <t>BOM CONSELHO</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>40168482000108</t>
+          <t>20885271000189</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SUPER COMPRAS SUPERMERCADO LTDA</t>
+          <t>L M GAS E TRANSPORTES LTDA</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>1621</v>
+        <v>1488926.54</v>
       </c>
     </row>
     <row r="123">
@@ -3871,28 +3883,28 @@
         <v>2026</v>
       </c>
       <c r="B123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C123" t="n">
-        <v>319</v>
+        <v>364</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>MACEIO</t>
+          <t>SAO MIGUEL DOS CAMPOS</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>41160020000107</t>
+          <t>45226498000143</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>OLIVEIRA E OLIVEIRA LTDA</t>
+          <t>AM SUPERMERCADO LTDA</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>1013.35</v>
+        <v>1612.98</v>
       </c>
     </row>
     <row r="124">
@@ -3900,28 +3912,28 @@
         <v>2026</v>
       </c>
       <c r="B124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C124" t="n">
-        <v>321</v>
+        <v>373</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>MACEIO</t>
+          <t>RIO LARGO</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>41916574000191</t>
+          <t>29981488000167</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>MGA AGENCIA DIGITAL LTDA</t>
+          <t>JOSIVALDO SOUZA DA SILVA E CIA LTDA</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>147.72</v>
+        <v>151402.11</v>
       </c>
     </row>
     <row r="125">
@@ -3929,10 +3941,10 @@
         <v>2026</v>
       </c>
       <c r="B125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C125" t="n">
-        <v>322</v>
+        <v>378</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -3941,16 +3953,16 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>41967862000175</t>
+          <t>40565135000119</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>COSTA MELO SOLUCOES EMPRESARIAIS LTDA</t>
+          <t>I S DO NASCIMENTO LTDA</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>2838.16</v>
+        <v>12935.44</v>
       </c>
     </row>
     <row r="126">
@@ -3958,10 +3970,10 @@
         <v>2026</v>
       </c>
       <c r="B126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C126" t="n">
-        <v>325</v>
+        <v>379</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -3970,16 +3982,16 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>42359515000122</t>
+          <t>45751076000197</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>BELLA VIDA ADMINISTRADORA LTDA</t>
+          <t>H MED ORTOPEDIA LTDA</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>233.24</v>
+        <v>66830.69</v>
       </c>
     </row>
     <row r="127">
@@ -3987,28 +3999,28 @@
         <v>2026</v>
       </c>
       <c r="B127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C127" t="n">
-        <v>326</v>
+        <v>382</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>MACEIO</t>
+          <t>RIO LARGO</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>42642452000117</t>
+          <t>26932502000144</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>AURICHERLA DA G. BARROS COMERCIO DE ALIM</t>
+          <t>JOSENILDA SOUZA DE LIMA</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>917105.3199999999</v>
+        <v>493.03</v>
       </c>
     </row>
     <row r="128">
@@ -4016,28 +4028,28 @@
         <v>2026</v>
       </c>
       <c r="B128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C128" t="n">
-        <v>328</v>
+        <v>383</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>PAULO AFONSO</t>
+          <t>SAO MIGUEL DOS CAMPOS</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>43173916000156</t>
+          <t>46813435000156</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>A. C. RODRIGUES MATOS SILVA</t>
+          <t>SANTOS PRESTADORA DE SERVICOS LTDA</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>518545.56</v>
+        <v>16.59</v>
       </c>
     </row>
     <row r="129">
@@ -4045,10 +4057,10 @@
         <v>2026</v>
       </c>
       <c r="B129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C129" t="n">
-        <v>331</v>
+        <v>386</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -4057,16 +4069,16 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>16690055000100</t>
+          <t>23732425000190</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>BOMBONIERE BRASIL DOCE LTDA</t>
+          <t>PAULO SIDNEY CARVALHO DE SOUZA</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>410921.15</v>
+        <v>314588.19</v>
       </c>
     </row>
     <row r="130">
@@ -4074,28 +4086,28 @@
         <v>2026</v>
       </c>
       <c r="B130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C130" t="n">
-        <v>334</v>
+        <v>387</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ARACAJU</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>13161435000160</t>
+          <t>33126577000101</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>AGROVEL AGRICULTURA E VETERINÁRIA LTDA</t>
+          <t>CENTRAL DA PANIFICACAO LTDA</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>66434.24000000001</v>
+        <v>347064.85</v>
       </c>
     </row>
     <row r="131">
@@ -4103,28 +4115,28 @@
         <v>2026</v>
       </c>
       <c r="B131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C131" t="n">
-        <v>336</v>
+        <v>390</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ARACAJU</t>
+          <t>CRAIBAS</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>32853772000162</t>
+          <t>46878268000121</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SERIGY BRICOLAGEM LTDA</t>
+          <t>CAMPO NOVO AGRO SOLUCOES LTDA</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>178849.68</v>
+        <v>96680.89</v>
       </c>
     </row>
     <row r="132">
@@ -4132,28 +4144,28 @@
         <v>2026</v>
       </c>
       <c r="B132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C132" t="n">
-        <v>337</v>
+        <v>391</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ARACAJU</t>
+          <t>PALMEIRA DOS INDIOS</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>32607758000189</t>
+          <t>46723837000160</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SERIGY SERVIÇOS EIRELI</t>
+          <t>COMERCIAL AGUA VIVA LTDA</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>393.88</v>
+        <v>70403.05</v>
       </c>
     </row>
     <row r="133">
@@ -4161,28 +4173,28 @@
         <v>2026</v>
       </c>
       <c r="B133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C133" t="n">
-        <v>338</v>
+        <v>401</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ARAPIRACA</t>
+          <t>SAO MIGUEL DOS CAMPOS</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>26277646000104</t>
+          <t>47911849000180</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>I R DANTAS DE BRITO E CIA LTDA</t>
+          <t>CARDAN SAO MIGUEL SERVICOS LTDA</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>810.5</v>
+        <v>32873.97</v>
       </c>
     </row>
     <row r="134">
@@ -4190,28 +4202,28 @@
         <v>2026</v>
       </c>
       <c r="B134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C134" t="n">
-        <v>339</v>
+        <v>409</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>MESSIAS</t>
+          <t>SAO MIGUEL DOS CAMPOS</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>43946463000153</t>
+          <t>46963300000177</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>MAC ALIMENTOS LTDA</t>
+          <t>MATRIZ MATERIAL DE CONSTRUCAO LTDA</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>521226.04</v>
+        <v>17999</v>
       </c>
     </row>
     <row r="135">
@@ -4219,28 +4231,28 @@
         <v>2026</v>
       </c>
       <c r="B135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C135" t="n">
-        <v>341</v>
+        <v>412</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>SATUBA</t>
+          <t>UNIAO DOS PALMARES</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>11330714000184</t>
+          <t>24327850000167</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>JOSE DA SILVA ALMEIDA</t>
+          <t>SUPERMERCADO ECONOMICO UNIAO LTDA</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>153786.78</v>
+        <v>420000</v>
       </c>
     </row>
     <row r="136">
@@ -4248,28 +4260,28 @@
         <v>2026</v>
       </c>
       <c r="B136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C136" t="n">
-        <v>342</v>
+        <v>414</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LAGARTO</t>
+          <t>BOM CONSELHO</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>16881386000128</t>
+          <t>49134652000108</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>ACO BOMPRECO COMERCIAL LAGARTO LTDA</t>
+          <t>FOCUS GESTÃO LTDA</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>510315.73</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="137">
@@ -4277,28 +4289,28 @@
         <v>2026</v>
       </c>
       <c r="B137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C137" t="n">
-        <v>345</v>
+        <v>419</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ARACAJU</t>
+          <t>ARAPIRACA</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>37539899000125</t>
+          <t>01492009000120</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>NUTRIAGRO COMERCIO DE MEDICAMENTOS VETER</t>
+          <t>ASSOCIACAO PESTALOZZI DE ARAPIRACA</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>731205.7</v>
+        <v>148740.04</v>
       </c>
     </row>
     <row r="138">
@@ -4306,28 +4318,24 @@
         <v>2026</v>
       </c>
       <c r="B138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C138" t="n">
-        <v>348</v>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>MACEIO</t>
-        </is>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>44432729000102</t>
+          <t>13161435000402</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>COMERCIAL ATACADISTA DE ACO E FERRO LTDA</t>
+          <t>AGROVEL AGRICULTURA E VETERINARIA LTDA</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>320253.94</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="139">
@@ -4335,28 +4343,24 @@
         <v>2026</v>
       </c>
       <c r="B139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C139" t="n">
-        <v>353</v>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>MACEIO</t>
-        </is>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>26678956000130</t>
+          <t>16690055000372</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>J R A PARAFUSOS MAQUINAS E FERRAMENTAS L</t>
+          <t>BOMBONIERE BRASIL DOCE LTDA</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>115622.96</v>
+        <v>86192.56</v>
       </c>
     </row>
     <row r="140">
@@ -4364,28 +4368,24 @@
         <v>2026</v>
       </c>
       <c r="B140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C140" t="n">
-        <v>355</v>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>BOM CONSELHO</t>
-        </is>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>17370582000109</t>
+          <t>11330714000265</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>AGROVAN COMERCIO VAREJISTA DE AVES LTDA</t>
+          <t>JOSE DA SILVA ALMEIDA</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>2124230.89</v>
+        <v>942195.08</v>
       </c>
     </row>
     <row r="141">
@@ -4393,28 +4393,24 @@
         <v>2026</v>
       </c>
       <c r="B141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C141" t="n">
-        <v>356</v>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>SANTA ROSA DE LIMA</t>
-        </is>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>03884414500371</t>
+          <t>10812956000222</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>CARLOS WALDEMAR DE ALMEIDA DANTAS</t>
+          <t>AMAZONPLAC COMERCIO DE MADEIRAS LTDA</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>266050</v>
+        <v>89244.33</v>
       </c>
     </row>
     <row r="142">
@@ -4422,28 +4418,24 @@
         <v>2026</v>
       </c>
       <c r="B142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C142" t="n">
-        <v>358</v>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>SANTANA DO SAO FRANCISCO</t>
-        </is>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>14891277000166</t>
+          <t>12207619000231</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>FRANKLIN BRUNO OLIVEIRA SANTA ROSA</t>
+          <t>RENATO CAVALCANTE LINS</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>222404.4</v>
+        <v>468006.99</v>
       </c>
     </row>
     <row r="143">
@@ -4451,28 +4443,24 @@
         <v>2026</v>
       </c>
       <c r="B143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C143" t="n">
-        <v>359</v>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>BOM CONSELHO</t>
-        </is>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>20885271000189</t>
+          <t>42642452000206</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>L M GAS E TRANSPORTES LTDA</t>
+          <t>AURICHERLA DA G. BARROS COMERCIO DE ALIM</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>2079930.49</v>
+        <v>432422.45</v>
       </c>
     </row>
     <row r="144">
@@ -4480,28 +4468,24 @@
         <v>2026</v>
       </c>
       <c r="B144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C144" t="n">
-        <v>364</v>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>SAO MIGUEL DOS CAMPOS</t>
-        </is>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>45226498000143</t>
+          <t>16690055000291</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>AM SUPERMERCADO LTDA</t>
+          <t>BOMBONIERE BRASIL DOCE LTDA</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>8.199999999999999</v>
+        <v>340807.01</v>
       </c>
     </row>
     <row r="145">
@@ -4509,28 +4493,24 @@
         <v>2026</v>
       </c>
       <c r="B145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C145" t="n">
-        <v>373</v>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>RIO LARGO</t>
-        </is>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>29981488000167</t>
+          <t>32853772000243</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>JOSIVALDO SOUZA DA SILVA E CIA LTDA</t>
+          <t>SERIGY BRICOLAGEM LTDA</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>199093.93</v>
+        <v>578481.47</v>
       </c>
     </row>
     <row r="146">
@@ -4538,28 +4518,24 @@
         <v>2026</v>
       </c>
       <c r="B146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C146" t="n">
-        <v>374</v>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>MACEIO</t>
-        </is>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>46290475000160</t>
+          <t>18151612000302</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>A. S. CORREIA ADMINISTRADORA LTDA</t>
+          <t>CASSIO EWERTON ALVES LACERDA</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>1134.7</v>
+        <v>17789.79</v>
       </c>
     </row>
     <row r="147">
@@ -4567,28 +4543,24 @@
         <v>2026</v>
       </c>
       <c r="B147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C147" t="n">
-        <v>378</v>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>ARAPIRACA</t>
-        </is>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>40565135000119</t>
+          <t>34073492000329</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>I S DO NASCIMENTO LTDA</t>
+          <t>GEOVANNE GOMES DOS SANTOS LTDA</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>47735.21</v>
+        <v>10544.36</v>
       </c>
     </row>
     <row r="148">
@@ -4596,28 +4568,28 @@
         <v>2026</v>
       </c>
       <c r="B148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C148" t="n">
-        <v>379</v>
+        <v>482</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ARAPIRACA</t>
+          <t>JAPOATA</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>45751076000197</t>
+          <t>08686395000130</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>H MED ORTOPEDIA LTDA</t>
+          <t>GS SUPERMERCADO LTDA</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>88148.00999999999</v>
+        <v>67238.41</v>
       </c>
     </row>
     <row r="149">
@@ -4625,28 +4597,28 @@
         <v>2026</v>
       </c>
       <c r="B149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C149" t="n">
-        <v>383</v>
+        <v>483</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>SAO MIGUEL DOS CAMPOS</t>
+          <t>BREJO GRANDE</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>46813435000156</t>
+          <t>14148171000177</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SANTOS PRESTADORA DE SERVICOS LTDA</t>
+          <t>ALENCAR ELETRO LTDA</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>430</v>
+        <v>5065.1</v>
       </c>
     </row>
     <row r="150">
@@ -4654,28 +4626,28 @@
         <v>2026</v>
       </c>
       <c r="B150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C150" t="n">
-        <v>386</v>
+        <v>484</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>MACEIO</t>
+          <t>BREJO GRANDE</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>23732425000190</t>
+          <t>09160038000104</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>PAULO SIDNEY CARVALHO DE SOUZA</t>
+          <t>ALENCAR ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>295198.73</v>
+        <v>116237.43</v>
       </c>
     </row>
     <row r="151">
@@ -4683,28 +4655,28 @@
         <v>2026</v>
       </c>
       <c r="B151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C151" t="n">
-        <v>387</v>
+        <v>487</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>MACEIO</t>
+          <t>NEOPOLIS</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>33126577000101</t>
+          <t>01522757000108</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>CENTRAL DA PANIFICACAO LTDA</t>
+          <t>SILVIA ALBUQUERQUE DE RESENDE CRUZ</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>711344.73</v>
+        <v>191502.13</v>
       </c>
     </row>
     <row r="152">
@@ -4712,28 +4684,28 @@
         <v>2026</v>
       </c>
       <c r="B152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C152" t="n">
-        <v>389</v>
+        <v>489</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>CORURIPE</t>
+          <t>ARACAJU</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>04362179000188</t>
+          <t>42268476000158</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>H V DE OLIVEIRA JUNIOR SUPERMERCADO LTDA</t>
+          <t>GRUPO AGROVEL LTDA</t>
         </is>
       </c>
       <c r="G152" t="n">
-        <v>276605.31</v>
+        <v>150</v>
       </c>
     </row>
     <row r="153">
@@ -4741,28 +4713,24 @@
         <v>2026</v>
       </c>
       <c r="B153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C153" t="n">
-        <v>390</v>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>CRAIBAS</t>
-        </is>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>46878268000121</t>
+          <t>32860231001729</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>CAMPO NOVO AGRO SOLUCOES LTDA</t>
+          <t>KI BARATO LTDA</t>
         </is>
       </c>
       <c r="G153" t="n">
-        <v>89409.61</v>
+        <v>3009342.84</v>
       </c>
     </row>
     <row r="154">
@@ -4770,28 +4738,24 @@
         <v>2026</v>
       </c>
       <c r="B154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C154" t="n">
-        <v>391</v>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>PALMEIRA DOS INDIOS</t>
-        </is>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>46723837000160</t>
+          <t>50304593000158</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUA VIVA LTDA</t>
+          <t>ED MATERIAIS DE CONSTRUCAO LTDA</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>117004.72</v>
+        <v>2334.7</v>
       </c>
     </row>
     <row r="155">
@@ -4799,28 +4763,24 @@
         <v>2026</v>
       </c>
       <c r="B155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C155" t="n">
-        <v>401</v>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>SAO MIGUEL DOS CAMPOS</t>
-        </is>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>47911849000180</t>
+          <t>44441644000190</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>CARDAN SAO MIGUEL SERVICOS LTDA</t>
+          <t>MARITIME SHIP SERVICE LOGISTICA LTDA</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>3292.36</v>
+        <v>1220347.21</v>
       </c>
     </row>
     <row r="156">
@@ -4828,28 +4788,24 @@
         <v>2026</v>
       </c>
       <c r="B156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C156" t="n">
-        <v>405</v>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>ARAPIRACA</t>
-        </is>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>24654991000194</t>
+          <t>51561578000158</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>LUNA SERVICOS MEDICOS LTDA</t>
+          <t>RESENDE CALCADOS E CONFECCOES LTDA</t>
         </is>
       </c>
       <c r="G156" t="n">
-        <v>11314.22</v>
+        <v>110575.67</v>
       </c>
     </row>
     <row r="157">
@@ -4857,28 +4813,24 @@
         <v>2026</v>
       </c>
       <c r="B157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C157" t="n">
-        <v>406</v>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>ARAPIRACA</t>
-        </is>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>48326648000189</t>
+          <t>46847173000140</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>TINA BABY MODA LTDA</t>
+          <t>JOSE ROBSON MARQUES DA SILVA LTDA</t>
         </is>
       </c>
       <c r="G157" t="n">
-        <v>11725.7</v>
+        <v>16070.78</v>
       </c>
     </row>
     <row r="158">
@@ -4886,28 +4838,24 @@
         <v>2026</v>
       </c>
       <c r="B158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C158" t="n">
-        <v>409</v>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>SAO MIGUEL DOS CAMPOS</t>
-        </is>
-      </c>
+        <v>519</v>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>46963300000177</t>
+          <t>12482836000159</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>MATRIZ MATERIAL DE CONSTRUCAO LTDA</t>
+          <t>VALDENICE BARROS E VALDIRENE BARROS</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>17990</v>
+        <v>173</v>
       </c>
     </row>
     <row r="159">
@@ -4915,28 +4863,24 @@
         <v>2026</v>
       </c>
       <c r="B159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C159" t="n">
-        <v>419</v>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>ARAPIRACA</t>
-        </is>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>01492009000120</t>
+          <t>05794150000642</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>ASSOCIACAO PESTALOZZI DE ARAPIRACA</t>
+          <t>AMANDA SIQUEIRA DE LIMA DANTAS LTDA</t>
         </is>
       </c>
       <c r="G159" t="n">
-        <v>87525.88</v>
+        <v>335530.34</v>
       </c>
     </row>
     <row r="160">
@@ -4944,24 +4888,24 @@
         <v>2026</v>
       </c>
       <c r="B160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C160" t="n">
-        <v>421</v>
+        <v>526</v>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>13161435000402</t>
+          <t>18614955000285</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>AGROVEL AGRICULTURA E VETERINARIA LTDA</t>
+          <t>PISEBEM COMERCIO DE REVESTIMENTO LTDA</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>12000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="161">
@@ -4969,24 +4913,24 @@
         <v>2026</v>
       </c>
       <c r="B161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C161" t="n">
-        <v>422</v>
+        <v>542</v>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>16690055000372</t>
+          <t>52005794000180</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>BOMBONIERE BRASIL DOCE LTDA</t>
+          <t>PEC CENTRO COMERCIO DE COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>123363.52</v>
+        <v>16354.16</v>
       </c>
     </row>
     <row r="162">
@@ -4994,24 +4938,24 @@
         <v>2026</v>
       </c>
       <c r="B162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C162" t="n">
-        <v>426</v>
+        <v>544</v>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>11330714000265</t>
+          <t>52506413000146</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>JOSE DA SILVA ALMEIDA</t>
+          <t>MUNDO DO MEDICO LTDA</t>
         </is>
       </c>
       <c r="G162" t="n">
-        <v>1120491.67</v>
+        <v>8558.5</v>
       </c>
     </row>
     <row r="163">
@@ -5019,24 +4963,24 @@
         <v>2026</v>
       </c>
       <c r="B163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C163" t="n">
-        <v>430</v>
+        <v>545</v>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>21640463000430</t>
+          <t>52427763000117</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>ACLECIO EVANGELISTA PEREIRA EIRELI</t>
+          <t>FALCAO ACQUA PARK LTDA</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>292202.17</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="164">
@@ -5044,24 +4988,24 @@
         <v>2026</v>
       </c>
       <c r="B164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C164" t="n">
-        <v>439</v>
+        <v>546</v>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>10812956000222</t>
+          <t>40770001000130</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>AMAZONPLAC COMERCIO DE MADEIRAS LTDA</t>
+          <t>CALDAS E LIMA SUPERMERCADO LTDA</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>91759</v>
+        <v>279128.91</v>
       </c>
     </row>
     <row r="165">
@@ -5069,24 +5013,24 @@
         <v>2026</v>
       </c>
       <c r="B165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C165" t="n">
-        <v>443</v>
+        <v>547</v>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>12207619000231</t>
+          <t>23268578000129</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>RENATO CAVALCANTE LINS</t>
+          <t xml:space="preserve">ALEXANDRE DE OLIVEIRA LEITAO ASSESSORIA </t>
         </is>
       </c>
       <c r="G165" t="n">
-        <v>532766.37</v>
+        <v>567.35</v>
       </c>
     </row>
     <row r="166">
@@ -5094,24 +5038,24 @@
         <v>2026</v>
       </c>
       <c r="B166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C166" t="n">
-        <v>445</v>
+        <v>551</v>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>20085483000262</t>
+          <t>48317392000143</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>J. J. AUGUSTINHO</t>
+          <t>RJ BERNARDES DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="G166" t="n">
-        <v>8150.65</v>
+        <v>83573.81</v>
       </c>
     </row>
     <row r="167">
@@ -5119,24 +5063,24 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C167" t="n">
-        <v>449</v>
+        <v>556</v>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>20085483000343</t>
+          <t>26597248000175</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>J. J. AUGUSTINHO</t>
+          <t>ANDRESSA TARGINO CARVALHO - SOCIEDADE IN</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>155097.42</v>
+        <v>2049.84</v>
       </c>
     </row>
     <row r="168">
@@ -5144,24 +5088,24 @@
         <v>2026</v>
       </c>
       <c r="B168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C168" t="n">
-        <v>450</v>
+        <v>557</v>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>18151612000221</t>
+          <t>52909258000109</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>CASSIO EWERTON ALVES LACERDA</t>
+          <t>SEVERO E OLIVEIRA COMERCIO DE GAS LTDA</t>
         </is>
       </c>
       <c r="G168" t="n">
-        <v>11559</v>
+        <v>7413.64</v>
       </c>
     </row>
     <row r="169">
@@ -5169,24 +5113,24 @@
         <v>2026</v>
       </c>
       <c r="B169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C169" t="n">
-        <v>456</v>
+        <v>559</v>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>42642452000206</t>
+          <t>20077977000114</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>AURICHERLA DA G. BARROS COMERCIO DE ALIM</t>
+          <t>MEGA MOTOS E-COMMERCE DE PECAS E ACESSOR</t>
         </is>
       </c>
       <c r="G169" t="n">
-        <v>639406.8</v>
+        <v>68880.03</v>
       </c>
     </row>
     <row r="170">
@@ -5194,24 +5138,24 @@
         <v>2026</v>
       </c>
       <c r="B170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C170" t="n">
-        <v>459</v>
+        <v>560</v>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>16690055000291</t>
+          <t>20077977000548</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>BOMBONIERE BRASIL DOCE LTDA</t>
+          <t>MEGA MOTOS E-COMMERCE DE PECAS E ACESSOR</t>
         </is>
       </c>
       <c r="G170" t="n">
-        <v>375709.69</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="171">
@@ -5219,24 +5163,24 @@
         <v>2026</v>
       </c>
       <c r="B171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C171" t="n">
-        <v>463</v>
+        <v>568</v>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>32853772000243</t>
+          <t>09588258000206</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>SERIGY BRICOLAGEM LTDA</t>
+          <t>MARIA ELIANE DOS SANTOS VESTUARIO</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>683539.35</v>
+        <v>32309.4</v>
       </c>
     </row>
     <row r="172">
@@ -5244,24 +5188,24 @@
         <v>2026</v>
       </c>
       <c r="B172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C172" t="n">
-        <v>468</v>
+        <v>569</v>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>26678956000211</t>
+          <t>48995232000153</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>J R A PARAFUSOS MAQUINAS E FERRAMENTAS L</t>
+          <t>PRESTADORA DE SERVICO PRECO BAIXO LTDA</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>16847.61</v>
+        <v>319.63</v>
       </c>
     </row>
     <row r="173">
@@ -5269,24 +5213,24 @@
         <v>2026</v>
       </c>
       <c r="B173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C173" t="n">
-        <v>469</v>
+        <v>570</v>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>18151612000302</t>
+          <t>29515888000187</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CASSIO EWERTON ALVES LACERDA</t>
+          <t>CENTRO MEDICO DE DIAGNOSTICOS LTDA</t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>17299.71</v>
+        <v>95467.06</v>
       </c>
     </row>
     <row r="174">
@@ -5294,24 +5238,24 @@
         <v>2026</v>
       </c>
       <c r="B174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C174" t="n">
-        <v>472</v>
+        <v>575</v>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>21640463000350</t>
+          <t>32535490000117</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>ACLECIO EVANGELISTA PEREIRA EIRELI</t>
+          <t>SANTOS COMERCIO DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>192905.64</v>
+        <v>1386869.71</v>
       </c>
     </row>
     <row r="175">
@@ -5319,24 +5263,24 @@
         <v>2026</v>
       </c>
       <c r="B175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C175" t="n">
-        <v>474</v>
+        <v>578</v>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>34073492000329</t>
+          <t>20112854000177</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>GEOVANNE GOMES DOS SANTOS LTDA</t>
+          <t>J J RODRIGUES VIEIRA E CIA LTDA</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>15611.16</v>
+        <v>71374.10000000001</v>
       </c>
     </row>
     <row r="176">
@@ -5344,28 +5288,24 @@
         <v>2026</v>
       </c>
       <c r="B176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C176" t="n">
-        <v>482</v>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>JAPOATA</t>
-        </is>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>08686395000130</t>
+          <t>28112164000120</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>GS SUPERMERCADO LTDA</t>
+          <t>J &amp; J CONSTRUCOES E IRRIGACOES LTDA</t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>64840.27</v>
+        <v>53133.03</v>
       </c>
     </row>
     <row r="177">
@@ -5373,28 +5313,24 @@
         <v>2026</v>
       </c>
       <c r="B177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C177" t="n">
-        <v>483</v>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>BREJO GRANDE</t>
-        </is>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>14148171000177</t>
+          <t>21186468000273</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>ALENCAR ELETRO LTDA</t>
+          <t xml:space="preserve">LYRA E MONTEIRO COMERCIO DE EMBARCACOES </t>
         </is>
       </c>
       <c r="G177" t="n">
-        <v>5881.77</v>
+        <v>517356.38</v>
       </c>
     </row>
     <row r="178">
@@ -5402,28 +5338,24 @@
         <v>2026</v>
       </c>
       <c r="B178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C178" t="n">
-        <v>484</v>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>BREJO GRANDE</t>
-        </is>
-      </c>
+        <v>586</v>
+      </c>
+      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>09160038000104</t>
+          <t>18614955000366</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>ALENCAR ALIMENTOS LTDA</t>
+          <t>PISEBEM COMERCIO DE REVESTIMENTO LTDA</t>
         </is>
       </c>
       <c r="G178" t="n">
-        <v>142966.17</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="179">
@@ -5431,28 +5363,24 @@
         <v>2026</v>
       </c>
       <c r="B179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C179" t="n">
-        <v>485</v>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>ARACAJU</t>
-        </is>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>44070087000149</t>
+          <t>07558262000115</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>V. P. DE CASTRO LIMA TAVARES LTDA</t>
+          <t>BATISTAO SUPERMERCADO LTDA</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>93.17</v>
+        <v>101189.57</v>
       </c>
     </row>
     <row r="180">
@@ -5460,28 +5388,24 @@
         <v>2026</v>
       </c>
       <c r="B180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C180" t="n">
-        <v>487</v>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>NEOPOLIS</t>
-        </is>
-      </c>
+        <v>592</v>
+      </c>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>01522757000108</t>
+          <t>51581271000119</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>SILVIA ALBUQUERQUE DE RESENDE CRUZ</t>
+          <t>AGROCAMPOS LTDA</t>
         </is>
       </c>
       <c r="G180" t="n">
-        <v>74725.84</v>
+        <v>20879.82</v>
       </c>
     </row>
     <row r="181">
@@ -5489,28 +5413,24 @@
         <v>2026</v>
       </c>
       <c r="B181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C181" t="n">
-        <v>489</v>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>ARACAJU</t>
-        </is>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>42268476000158</t>
+          <t>53979615000178</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>GRUPO AGROVEL LTDA</t>
+          <t>LUIS LECIO ALVES DO AMARAL LTDA</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>150</v>
+        <v>7617.21</v>
       </c>
     </row>
     <row r="182">
@@ -5518,24 +5438,24 @@
         <v>2026</v>
       </c>
       <c r="B182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C182" t="n">
-        <v>496</v>
+        <v>597</v>
       </c>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>32860231001729</t>
+          <t>53749526000135</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>KI BARATO LTDA</t>
+          <t>C S GESTAO EMPRESARIAL LTDA</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>3630507.26</v>
+        <v>810.5</v>
       </c>
     </row>
     <row r="183">
@@ -5543,24 +5463,24 @@
         <v>2026</v>
       </c>
       <c r="B183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C183" t="n">
-        <v>497</v>
+        <v>605</v>
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>50304593000158</t>
+          <t>32999833000102</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>ED MATERIAIS DE CONSTRUCAO LTDA</t>
+          <t>SILVA SUPERMERCADO LTDA</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>2861.56</v>
+        <v>303473.51</v>
       </c>
     </row>
     <row r="184">
@@ -5568,24 +5488,24 @@
         <v>2026</v>
       </c>
       <c r="B184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C184" t="n">
-        <v>498</v>
+        <v>612</v>
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>44441644000190</t>
+          <t>54328246000116</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>MARITIME SHIP SERVICE LOGISTICA LTDA</t>
+          <t>JK SANTOS ADMINISTRADORA LTDA</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>1395455.3</v>
+        <v>755</v>
       </c>
     </row>
     <row r="185">
@@ -5593,24 +5513,24 @@
         <v>2026</v>
       </c>
       <c r="B185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C185" t="n">
-        <v>512</v>
+        <v>613</v>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>51561578000158</t>
+          <t>54493161000193</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>RESENDE CALCADOS E CONFECCOES LTDA</t>
+          <t>SUPER MARTINS LTDA</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>42144.89</v>
+        <v>170952.32</v>
       </c>
     </row>
     <row r="186">
@@ -5618,24 +5538,24 @@
         <v>2026</v>
       </c>
       <c r="B186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C186" t="n">
-        <v>518</v>
+        <v>614</v>
       </c>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>46847173000140</t>
+          <t>54455272000105</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>JOSE ROBSON MARQUES DA SILVA LTDA</t>
+          <t>UMBEER UNIAO MIRANDA BEER LTDA</t>
         </is>
       </c>
       <c r="G186" t="n">
-        <v>24161.53</v>
+        <v>204422.85</v>
       </c>
     </row>
     <row r="187">
@@ -5643,24 +5563,24 @@
         <v>2026</v>
       </c>
       <c r="B187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C187" t="n">
-        <v>519</v>
+        <v>636</v>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>12482836000159</t>
+          <t>41483782000144</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>VALDENICE BARROS E VALDIRENE BARROS</t>
+          <t>PANIFICACAO ALVORADA III LTDA</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>654.67</v>
+        <v>251339.14</v>
       </c>
     </row>
     <row r="188">
@@ -5668,24 +5588,24 @@
         <v>2026</v>
       </c>
       <c r="B188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C188" t="n">
-        <v>524</v>
+        <v>637</v>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>05794150000642</t>
+          <t>08611323000123</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>AMANDA SIQUEIRA DE LIMA DANTAS LTDA</t>
+          <t>ALAYN KLEBER FREIRE DA SILVA LTDA</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>940972.13</v>
+        <v>26140.2</v>
       </c>
     </row>
     <row r="189">
@@ -5693,24 +5613,24 @@
         <v>2026</v>
       </c>
       <c r="B189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C189" t="n">
-        <v>526</v>
+        <v>641</v>
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>18614955000285</t>
+          <t>32621975000395</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>PISEBEM COMERCIO DE REVESTIMENTO LTDA</t>
+          <t>S V S DE AQUINO E CIA LTDA</t>
         </is>
       </c>
       <c r="G189" t="n">
-        <v>54893.14</v>
+        <v>913591.3</v>
       </c>
     </row>
     <row r="190">
@@ -5718,24 +5638,24 @@
         <v>2026</v>
       </c>
       <c r="B190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C190" t="n">
-        <v>542</v>
+        <v>648</v>
       </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>52005794000180</t>
+          <t>55668856000121</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>PEC CENTRO COMERCIO DE COSMETICOS LTDA</t>
+          <t>R O DA SILVA ATACAREJO</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>20294.07</v>
+        <v>175029.1</v>
       </c>
     </row>
     <row r="191">
@@ -5743,24 +5663,24 @@
         <v>2026</v>
       </c>
       <c r="B191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C191" t="n">
-        <v>544</v>
+        <v>649</v>
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
-          <t>52506413000146</t>
+          <t>55868717000141</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>MUNDO DO MEDICO LTDA</t>
+          <t>SOUZA &amp; LIMA LTDA</t>
         </is>
       </c>
       <c r="G191" t="n">
-        <v>12454.09</v>
+        <v>50799.14</v>
       </c>
     </row>
     <row r="192">
@@ -5768,24 +5688,24 @@
         <v>2026</v>
       </c>
       <c r="B192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C192" t="n">
-        <v>546</v>
+        <v>650</v>
       </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
-          <t>40770001000130</t>
+          <t>34073492000400</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>CALDAS E LIMA SUPERMERCADO LTDA</t>
+          <t>GEOVANNE GOMES DOS SANTOS LTDA</t>
         </is>
       </c>
       <c r="G192" t="n">
-        <v>450091.81</v>
+        <v>10439.22</v>
       </c>
     </row>
     <row r="193">
@@ -5793,24 +5713,24 @@
         <v>2026</v>
       </c>
       <c r="B193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C193" t="n">
-        <v>551</v>
+        <v>651</v>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>48317392000143</t>
+          <t>46459824000125</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>RJ BERNARDES DISTRIBUIDORA LTDA</t>
+          <t>DH ORTOPEDIA LTDA</t>
         </is>
       </c>
       <c r="G193" t="n">
-        <v>35617.49</v>
+        <v>3079.9</v>
       </c>
     </row>
     <row r="194">
@@ -5818,24 +5738,24 @@
         <v>2026</v>
       </c>
       <c r="B194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C194" t="n">
-        <v>556</v>
+        <v>661</v>
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>26597248000175</t>
+          <t>32860231001800</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>ANDRESSA TARGINO CARVALHO - SOCIEDADE IN</t>
+          <t>KI BARATO LTDA</t>
         </is>
       </c>
       <c r="G194" t="n">
-        <v>337</v>
+        <v>1327816.04</v>
       </c>
     </row>
     <row r="195">
@@ -5843,24 +5763,24 @@
         <v>2026</v>
       </c>
       <c r="B195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C195" t="n">
-        <v>557</v>
+        <v>664</v>
       </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>52909258000109</t>
+          <t>55888894000190</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>SEVERO E OLIVEIRA COMERCIO DE GAS LTDA</t>
+          <t>CLINICA MELYNA PESSOA LTDA</t>
         </is>
       </c>
       <c r="G195" t="n">
-        <v>332064.96</v>
+        <v>11215.32</v>
       </c>
     </row>
     <row r="196">
@@ -5868,24 +5788,24 @@
         <v>2026</v>
       </c>
       <c r="B196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C196" t="n">
-        <v>559</v>
+        <v>665</v>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>20077977000114</t>
+          <t>22664506000138</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>MEGA MOTOS E-COMMERCE DE PECAS E ACESSOR</t>
+          <t>COMERCIAL DE ALIMENTOS GLOBO LTDA</t>
         </is>
       </c>
       <c r="G196" t="n">
-        <v>38502.23</v>
+        <v>2707336.44</v>
       </c>
     </row>
     <row r="197">
@@ -5893,24 +5813,24 @@
         <v>2026</v>
       </c>
       <c r="B197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C197" t="n">
-        <v>560</v>
+        <v>666</v>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>20077977000548</t>
+          <t>46722786000151</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>MEGA MOTOS E-COMMERCE DE PECAS E ACESSOR</t>
+          <t>LETICIA C L COSTA LTDA</t>
         </is>
       </c>
       <c r="G197" t="n">
-        <v>89050.38</v>
+        <v>135.93</v>
       </c>
     </row>
     <row r="198">
@@ -5918,24 +5838,24 @@
         <v>2026</v>
       </c>
       <c r="B198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C198" t="n">
-        <v>568</v>
+        <v>667</v>
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>09588258000206</t>
+          <t>46642854000172</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>MARIA ELIANE DOS SANTOS VESTUARIO</t>
+          <t>MEDCORP SERVICOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="G198" t="n">
-        <v>31183.6</v>
+        <v>810.5</v>
       </c>
     </row>
     <row r="199">
@@ -5943,24 +5863,24 @@
         <v>2026</v>
       </c>
       <c r="B199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C199" t="n">
-        <v>569</v>
+        <v>669</v>
       </c>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>48995232000153</t>
+          <t>22664506000308</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>PRESTADORA DE SERVICO PRECO BAIXO LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS GLOBO LTDA</t>
         </is>
       </c>
       <c r="G199" t="n">
-        <v>319.63</v>
+        <v>866799.49</v>
       </c>
     </row>
     <row r="200">
@@ -5968,24 +5888,24 @@
         <v>2026</v>
       </c>
       <c r="B200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C200" t="n">
-        <v>570</v>
+        <v>670</v>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>29515888000187</t>
+          <t>21603375000116</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO DE DIAGNOSTICOS LTDA</t>
+          <t>ATACAREJO BOA ESPERANCA LTDA</t>
         </is>
       </c>
       <c r="G200" t="n">
-        <v>28673.84</v>
+        <v>4816432.34</v>
       </c>
     </row>
     <row r="201">
@@ -5993,24 +5913,24 @@
         <v>2026</v>
       </c>
       <c r="B201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C201" t="n">
-        <v>575</v>
+        <v>672</v>
       </c>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>32535490000117</t>
+          <t>49382063000149</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>SANTOS COMERCIO DE ALIMENTOS LTDA</t>
+          <t>MERCADINHO QUINZE DE NOVEMBRO LTDA</t>
         </is>
       </c>
       <c r="G201" t="n">
-        <v>1279810.66</v>
+        <v>375377.8</v>
       </c>
     </row>
     <row r="202">
@@ -6018,24 +5938,24 @@
         <v>2026</v>
       </c>
       <c r="B202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C202" t="n">
-        <v>578</v>
+        <v>675</v>
       </c>
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>20112854000177</t>
+          <t>02668289000147</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>J J RODRIGUES VIEIRA E CIA LTDA</t>
+          <t>F. A. DA SILVA LTDA</t>
         </is>
       </c>
       <c r="G202" t="n">
-        <v>4780.49</v>
+        <v>751518.85</v>
       </c>
     </row>
     <row r="203">
@@ -6043,24 +5963,24 @@
         <v>2026</v>
       </c>
       <c r="B203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C203" t="n">
-        <v>580</v>
+        <v>683</v>
       </c>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>28112164000120</t>
+          <t>15696129000153</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>J &amp; J CONSTRUCOES E IRRIGACOES LTDA</t>
+          <t>AUTO POSTO GLOBO LTDA</t>
         </is>
       </c>
       <c r="G203" t="n">
-        <v>123350.86</v>
+        <v>1149544.96</v>
       </c>
     </row>
     <row r="204">
@@ -6068,24 +5988,24 @@
         <v>2026</v>
       </c>
       <c r="B204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C204" t="n">
-        <v>581</v>
+        <v>685</v>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>21186468000273</t>
+          <t>25294255000135</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">LYRA E MONTEIRO COMERCIO DE EMBARCACOES </t>
+          <t>AUTO POSTO GLOBO II LTDA</t>
         </is>
       </c>
       <c r="G204" t="n">
-        <v>1416350.96</v>
+        <v>174711.14</v>
       </c>
     </row>
     <row r="205">
@@ -6093,24 +6013,24 @@
         <v>2026</v>
       </c>
       <c r="B205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C205" t="n">
-        <v>586</v>
+        <v>686</v>
       </c>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>18614955000366</t>
+          <t>30934089000124</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>PISEBEM COMERCIO DE REVESTIMENTO LTDA</t>
+          <t>AUTO POSTO GLOBO IV LTDA</t>
         </is>
       </c>
       <c r="G205" t="n">
-        <v>103662.99</v>
+        <v>104970.96</v>
       </c>
     </row>
     <row r="206">
@@ -6118,24 +6038,24 @@
         <v>2026</v>
       </c>
       <c r="B206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C206" t="n">
-        <v>590</v>
+        <v>687</v>
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
-          <t>07558262000115</t>
+          <t>29766200000131</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>BATISTAO SUPERMERCADO LTDA</t>
+          <t>AUTO POSTO GLOBO III LTDA</t>
         </is>
       </c>
       <c r="G206" t="n">
-        <v>575348.22</v>
+        <v>28001</v>
       </c>
     </row>
     <row r="207">
@@ -6143,24 +6063,24 @@
         <v>2026</v>
       </c>
       <c r="B207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C207" t="n">
-        <v>592</v>
+        <v>690</v>
       </c>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
-          <t>51581271000119</t>
+          <t>57643301000150</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>AGROCAMPOS LTDA</t>
+          <t>PGS ALIMENTOS E BEBIDAS LTDA</t>
         </is>
       </c>
       <c r="G207" t="n">
-        <v>17454.9</v>
+        <v>2563942.39</v>
       </c>
     </row>
     <row r="208">
@@ -6168,24 +6088,24 @@
         <v>2026</v>
       </c>
       <c r="B208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C208" t="n">
-        <v>596</v>
+        <v>694</v>
       </c>
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
-          <t>53979615000178</t>
+          <t>57409432000178</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>LUIS LECIO ALVES DO AMARAL LTDA</t>
+          <t>VAREJO CONECTADO CONSULTING LTDA</t>
         </is>
       </c>
       <c r="G208" t="n">
-        <v>20834.59</v>
+        <v>309</v>
       </c>
     </row>
     <row r="209">
@@ -6193,24 +6113,24 @@
         <v>2026</v>
       </c>
       <c r="B209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C209" t="n">
-        <v>597</v>
+        <v>695</v>
       </c>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
-          <t>53749526000135</t>
+          <t>28215252000157</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>C S GESTAO EMPRESARIAL LTDA</t>
+          <t>RESENDE SUPERMERCADO LTDA</t>
         </is>
       </c>
       <c r="G209" t="n">
-        <v>845.5</v>
+        <v>333583.32</v>
       </c>
     </row>
     <row r="210">
@@ -6218,24 +6138,24 @@
         <v>2026</v>
       </c>
       <c r="B210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C210" t="n">
-        <v>605</v>
+        <v>698</v>
       </c>
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
-          <t>32999833000102</t>
+          <t>18614955000447</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>SILVA SUPERMERCADO LTDA</t>
+          <t>PISEBEM COMERCIO DE REVESTIMENTO LTDA</t>
         </is>
       </c>
       <c r="G210" t="n">
-        <v>256449.87</v>
+        <v>100000.21</v>
       </c>
     </row>
     <row r="211">
@@ -6243,24 +6163,24 @@
         <v>2026</v>
       </c>
       <c r="B211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C211" t="n">
-        <v>613</v>
+        <v>703</v>
       </c>
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
-          <t>54493161000193</t>
+          <t>57799882000114</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>SUPER MARTINS LTDA</t>
+          <t xml:space="preserve">MEGA MOTOS COMERCIO DE PECAS E SERVICOS </t>
         </is>
       </c>
       <c r="G211" t="n">
-        <v>161030</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="212">
@@ -6268,24 +6188,24 @@
         <v>2026</v>
       </c>
       <c r="B212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C212" t="n">
-        <v>614</v>
+        <v>710</v>
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
-          <t>54455272000105</t>
+          <t>45433635000110</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>UMBEER UNIAO MIRANDA BEER LTDA</t>
+          <t>BEM NATU ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="G212" t="n">
-        <v>17800650.66</v>
+        <v>40424.5</v>
       </c>
     </row>
     <row r="213">
@@ -6293,24 +6213,24 @@
         <v>2026</v>
       </c>
       <c r="B213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C213" t="n">
-        <v>636</v>
+        <v>712</v>
       </c>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
-          <t>41483782000144</t>
+          <t>14079987000196</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>PANIFICACAO ALVORADA III LTDA</t>
+          <t>M C A DE OLIVEIRA LIMA</t>
         </is>
       </c>
       <c r="G213" t="n">
-        <v>467675.14</v>
+        <v>474631.78</v>
       </c>
     </row>
     <row r="214">
@@ -6318,24 +6238,24 @@
         <v>2026</v>
       </c>
       <c r="B214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C214" t="n">
-        <v>637</v>
+        <v>714</v>
       </c>
       <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
-          <t>08611323000123</t>
+          <t>32535490000206</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>ALAYN KLEBER FREIRE DA SILVA LTDA</t>
+          <t>SANTOS COMERCIO DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="G214" t="n">
-        <v>11857.67</v>
+        <v>1267612.43</v>
       </c>
     </row>
     <row r="215">
@@ -6343,24 +6263,24 @@
         <v>2026</v>
       </c>
       <c r="B215" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C215" t="n">
-        <v>641</v>
+        <v>715</v>
       </c>
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
-          <t>32621975000395</t>
+          <t>35229626000159</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>S V S DE AQUINO E CIA LTDA</t>
+          <t>BARBOSA CARVALHO COMERCIO VAREJISTA DE P</t>
         </is>
       </c>
       <c r="G215" t="n">
-        <v>1727447.66</v>
+        <v>590749.52</v>
       </c>
     </row>
     <row r="216">
@@ -6368,24 +6288,24 @@
         <v>2026</v>
       </c>
       <c r="B216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C216" t="n">
-        <v>644</v>
+        <v>717</v>
       </c>
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
-          <t>55891307000111</t>
+          <t>49691436000163</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>MARITIME SAFETY SERVICE LTDA</t>
+          <t>BARBOSA BARBOSA COMERCIO VAREJISTA DE AL</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>255</v>
+        <v>47445.98</v>
       </c>
     </row>
     <row r="217">
@@ -6393,24 +6313,24 @@
         <v>2026</v>
       </c>
       <c r="B217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C217" t="n">
-        <v>648</v>
+        <v>720</v>
       </c>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr">
         <is>
-          <t>55668856000121</t>
+          <t>32535490000389</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>R O DA SILVA ATACAREJO</t>
+          <t>SANTOS COMERCIO DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="G217" t="n">
-        <v>153572.09</v>
+        <v>1193013.75</v>
       </c>
     </row>
     <row r="218">
@@ -6418,24 +6338,24 @@
         <v>2026</v>
       </c>
       <c r="B218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C218" t="n">
-        <v>649</v>
+        <v>725</v>
       </c>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
-          <t>55868717000141</t>
+          <t>43623019000105</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>SOUZA &amp; LIMA LTDA</t>
+          <t>DARLAN C DO CARMO</t>
         </is>
       </c>
       <c r="G218" t="n">
-        <v>68495.66</v>
+        <v>2431.5</v>
       </c>
     </row>
     <row r="219">
@@ -6443,24 +6363,24 @@
         <v>2026</v>
       </c>
       <c r="B219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C219" t="n">
-        <v>650</v>
+        <v>730</v>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
-          <t>34073492000400</t>
+          <t>16719046000103</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>GEOVANNE GOMES DOS SANTOS LTDA</t>
+          <t>MERCATTO PANIFICACAO &amp; CAFETERIA LTDA</t>
         </is>
       </c>
       <c r="G219" t="n">
-        <v>19854.68</v>
+        <v>541.5</v>
       </c>
     </row>
     <row r="220">
@@ -6468,24 +6388,24 @@
         <v>2026</v>
       </c>
       <c r="B220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C220" t="n">
-        <v>651</v>
+        <v>731</v>
       </c>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr">
         <is>
-          <t>46459824000125</t>
+          <t>35229626000230</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>DH ORTOPEDIA LTDA</t>
+          <t>BARBOSA CARVALHO COMERCIO VAREJISTA DE P</t>
         </is>
       </c>
       <c r="G220" t="n">
-        <v>3079.9</v>
+        <v>254406.93</v>
       </c>
     </row>
     <row r="221">
@@ -6493,24 +6413,24 @@
         <v>2026</v>
       </c>
       <c r="B221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C221" t="n">
-        <v>661</v>
+        <v>733</v>
       </c>
       <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr">
         <is>
-          <t>32860231001800</t>
+          <t>58457553000158</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>KI BARATO LTDA</t>
+          <t>ALVORADA LOCACAO LTDA</t>
         </is>
       </c>
       <c r="G221" t="n">
-        <v>998142.9399999999</v>
+        <v>182.54</v>
       </c>
     </row>
     <row r="222">
@@ -6518,24 +6438,24 @@
         <v>2026</v>
       </c>
       <c r="B222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C222" t="n">
-        <v>665</v>
+        <v>734</v>
       </c>
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
-          <t>22664506000138</t>
+          <t>53930552000165</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS GLOBO LTDA</t>
+          <t>ALIANCA ATACADO LTDA</t>
         </is>
       </c>
       <c r="G222" t="n">
-        <v>3670853.51</v>
+        <v>313807.76</v>
       </c>
     </row>
     <row r="223">
@@ -6543,24 +6463,24 @@
         <v>2026</v>
       </c>
       <c r="B223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C223" t="n">
-        <v>666</v>
+        <v>745</v>
       </c>
       <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr">
         <is>
-          <t>46722786000151</t>
+          <t>39270496000159</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>LETICIA C L COSTA LTDA</t>
+          <t>V B R COMERCIO DE FRUTAS LTDA</t>
         </is>
       </c>
       <c r="G223" t="n">
-        <v>6684.8</v>
+        <v>64398.61</v>
       </c>
     </row>
     <row r="224">
@@ -6568,24 +6488,24 @@
         <v>2026</v>
       </c>
       <c r="B224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C224" t="n">
-        <v>667</v>
+        <v>750</v>
       </c>
       <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr">
         <is>
-          <t>46642854000172</t>
+          <t>35824052000167</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>MEDCORP SERVICOS MEDICOS LTDA</t>
+          <t>UP TELECOM E SERVICOS LTDA</t>
         </is>
       </c>
       <c r="G224" t="n">
-        <v>2810.5</v>
+        <v>7101.51</v>
       </c>
     </row>
     <row r="225">
@@ -6593,24 +6513,24 @@
         <v>2026</v>
       </c>
       <c r="B225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C225" t="n">
-        <v>669</v>
+        <v>753</v>
       </c>
       <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
-          <t>22664506000308</t>
+          <t>59706743000124</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS GLOBO LTDA</t>
+          <t>LINS GENEROS ALIMENTICIOS LTDA</t>
         </is>
       </c>
       <c r="G225" t="n">
-        <v>1499173.16</v>
+        <v>350620.69</v>
       </c>
     </row>
     <row r="226">
@@ -6618,24 +6538,24 @@
         <v>2026</v>
       </c>
       <c r="B226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C226" t="n">
-        <v>670</v>
+        <v>755</v>
       </c>
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
-          <t>21603375000116</t>
+          <t>43663474000550</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>ATACAREJO BOA ESPERANCA LTDA</t>
+          <t>MELISSIA C HARDY LTDA</t>
         </is>
       </c>
       <c r="G226" t="n">
-        <v>4549136.26</v>
+        <v>34070.9</v>
       </c>
     </row>
     <row r="227">
@@ -6643,24 +6563,24 @@
         <v>2026</v>
       </c>
       <c r="B227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C227" t="n">
-        <v>672</v>
+        <v>756</v>
       </c>
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
-          <t>49382063000149</t>
+          <t>48681098000116</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>MERCADINHO QUINZE DE NOVEMBRO LTDA</t>
+          <t>SA RIBEIRO COMERCIO ALIMENTICIO LTDA</t>
         </is>
       </c>
       <c r="G227" t="n">
-        <v>247035.11</v>
+        <v>460461.1</v>
       </c>
     </row>
     <row r="228">
@@ -6668,24 +6588,24 @@
         <v>2026</v>
       </c>
       <c r="B228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C228" t="n">
-        <v>675</v>
+        <v>757</v>
       </c>
       <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
-          <t>02668289000147</t>
+          <t>54460259000144</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>F. A. DA SILVA LTDA</t>
+          <t>W K COSTA LEITE</t>
         </is>
       </c>
       <c r="G228" t="n">
-        <v>893028.73</v>
+        <v>790447.29</v>
       </c>
     </row>
     <row r="229">
@@ -6693,24 +6613,24 @@
         <v>2026</v>
       </c>
       <c r="B229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C229" t="n">
-        <v>676</v>
+        <v>758</v>
       </c>
       <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
-          <t>10731664000184</t>
+          <t>59685839000153</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>TRAJETORIA MAGAZINE LTDA</t>
+          <t>CLINICA VIOTTO MACEIO LTDA</t>
         </is>
       </c>
       <c r="G229" t="n">
-        <v>228538.32</v>
+        <v>2875.09</v>
       </c>
     </row>
     <row r="230">
@@ -6718,24 +6638,24 @@
         <v>2026</v>
       </c>
       <c r="B230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C230" t="n">
-        <v>680</v>
+        <v>759</v>
       </c>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
-          <t>02113134000144</t>
+          <t>59825964000111</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>E DO GLOBO TORRES MAGAZINE LTDA</t>
+          <t>PAIVA SANTOS LTDA</t>
         </is>
       </c>
       <c r="G230" t="n">
-        <v>145226.55</v>
+        <v>97781.96000000001</v>
       </c>
     </row>
     <row r="231">
@@ -6743,24 +6663,24 @@
         <v>2026</v>
       </c>
       <c r="B231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C231" t="n">
-        <v>683</v>
+        <v>760</v>
       </c>
       <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
-          <t>15696129000153</t>
+          <t>60126014000188</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>AUTO POSTO GLOBO LTDA</t>
+          <t>MAXX ATACAREJO COMERCIO DE ALIMENTOS LTD</t>
         </is>
       </c>
       <c r="G231" t="n">
-        <v>18658990.02</v>
+        <v>98588.92</v>
       </c>
     </row>
     <row r="232">
@@ -6768,24 +6688,24 @@
         <v>2026</v>
       </c>
       <c r="B232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C232" t="n">
-        <v>685</v>
+        <v>762</v>
       </c>
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
-          <t>25294255000135</t>
+          <t>07536029000131</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>AUTO POSTO GLOBO II LTDA</t>
+          <t>WILDSON XAVIER DA SILVA LTDA</t>
         </is>
       </c>
       <c r="G232" t="n">
-        <v>147296.77</v>
+        <v>445393.79</v>
       </c>
     </row>
     <row r="233">
@@ -6793,24 +6713,24 @@
         <v>2026</v>
       </c>
       <c r="B233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C233" t="n">
-        <v>686</v>
+        <v>769</v>
       </c>
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
-          <t>30934089000124</t>
+          <t>03339821000900</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>AUTO POSTO GLOBO IV LTDA</t>
+          <t>REVENDEDORA DE PNEUS TC LTDA.</t>
         </is>
       </c>
       <c r="G233" t="n">
-        <v>171520.97</v>
+        <v>255948.22</v>
       </c>
     </row>
     <row r="234">
@@ -6818,24 +6738,24 @@
         <v>2026</v>
       </c>
       <c r="B234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C234" t="n">
-        <v>687</v>
+        <v>770</v>
       </c>
       <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr">
         <is>
-          <t>29766200000131</t>
+          <t>03339821000145</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>AUTO POSTO GLOBO III LTDA</t>
+          <t>REVENDEDORA DE PNEUS TC LTDA.</t>
         </is>
       </c>
       <c r="G234" t="n">
-        <v>98814.12</v>
+        <v>128844.45</v>
       </c>
     </row>
     <row r="235">
@@ -6843,24 +6763,24 @@
         <v>2026</v>
       </c>
       <c r="B235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C235" t="n">
-        <v>690</v>
+        <v>771</v>
       </c>
       <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
-          <t>57643301000150</t>
+          <t>03339821000226</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>PGS ALIMENTOS E BEBIDAS LTDA</t>
+          <t>REVENDEDORA DE PNEUS TC LTDA.</t>
         </is>
       </c>
       <c r="G235" t="n">
-        <v>3336320.42</v>
+        <v>68165.64999999999</v>
       </c>
     </row>
     <row r="236">
@@ -6868,24 +6788,24 @@
         <v>2026</v>
       </c>
       <c r="B236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C236" t="n">
-        <v>695</v>
+        <v>772</v>
       </c>
       <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
-          <t>28215252000157</t>
+          <t>03339821000307</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>RESENDE SUPERMERCADO LTDA</t>
+          <t>REVENDEDORA DE PNEUS TC LTDA.</t>
         </is>
       </c>
       <c r="G236" t="n">
-        <v>295798.12</v>
+        <v>330313.66</v>
       </c>
     </row>
     <row r="237">
@@ -6893,24 +6813,24 @@
         <v>2026</v>
       </c>
       <c r="B237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C237" t="n">
-        <v>698</v>
+        <v>773</v>
       </c>
       <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
-          <t>18614955000447</t>
+          <t>03339821001036</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>PISEBEM COMERCIO DE REVESTIMENTO LTDA</t>
+          <t>REVENDEDORA DE PNEUS TC LTDA.</t>
         </is>
       </c>
       <c r="G237" t="n">
-        <v>103348.54</v>
+        <v>44146.32</v>
       </c>
     </row>
     <row r="238">
@@ -6918,24 +6838,24 @@
         <v>2026</v>
       </c>
       <c r="B238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C238" t="n">
-        <v>701</v>
+        <v>774</v>
       </c>
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
-          <t>57799882000203</t>
+          <t>03339821000730</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEGA MOTOS COMERCIO DE PECAS E SERVICOS </t>
+          <t>REVENDEDORA DE PNEUS TC LTDA.</t>
         </is>
       </c>
       <c r="G238" t="n">
-        <v>23382.69</v>
+        <v>550744.22</v>
       </c>
     </row>
     <row r="239">
@@ -6943,24 +6863,24 @@
         <v>2026</v>
       </c>
       <c r="B239" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C239" t="n">
-        <v>703</v>
+        <v>775</v>
       </c>
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
-          <t>57799882000114</t>
+          <t>03339821000811</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEGA MOTOS COMERCIO DE PECAS E SERVICOS </t>
+          <t>REVENDEDORA DE PNEUS TC LTDA.</t>
         </is>
       </c>
       <c r="G239" t="n">
-        <v>17046.36</v>
+        <v>141420.61</v>
       </c>
     </row>
     <row r="240">
@@ -6968,24 +6888,24 @@
         <v>2026</v>
       </c>
       <c r="B240" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C240" t="n">
-        <v>710</v>
+        <v>777</v>
       </c>
       <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
-          <t>45433635000110</t>
+          <t>60734656000160</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>BEM NATU ALIMENTOS LTDA</t>
+          <t>AMORIM E OLIVEIRA LOCADORA LTDA</t>
         </is>
       </c>
       <c r="G240" t="n">
-        <v>48228.01</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="241">
@@ -6993,24 +6913,24 @@
         <v>2026</v>
       </c>
       <c r="B241" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C241" t="n">
-        <v>712</v>
+        <v>783</v>
       </c>
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr">
         <is>
-          <t>14079987000196</t>
+          <t>52016958000174</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>M C A DE OLIVEIRA LIMA</t>
+          <t>SEVEN SUPERMERCADO LTDA</t>
         </is>
       </c>
       <c r="G241" t="n">
-        <v>569869.15</v>
+        <v>400307.3</v>
       </c>
     </row>
     <row r="242">
@@ -7018,24 +6938,24 @@
         <v>2026</v>
       </c>
       <c r="B242" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C242" t="n">
-        <v>714</v>
+        <v>785</v>
       </c>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
-          <t>32535490000206</t>
+          <t>61167515000175</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>SANTOS COMERCIO DE ALIMENTOS LTDA</t>
+          <t>LACERDA E BARBOSA LTDA</t>
         </is>
       </c>
       <c r="G242" t="n">
-        <v>1253745.53</v>
+        <v>5532.54</v>
       </c>
     </row>
     <row r="243">
@@ -7043,24 +6963,24 @@
         <v>2026</v>
       </c>
       <c r="B243" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C243" t="n">
-        <v>715</v>
+        <v>797</v>
       </c>
       <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
-          <t>35229626000159</t>
+          <t>61520245000134</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>BARBOSA CARVALHO COMERCIO VAREJISTA DE P</t>
+          <t>L L COMERCIO DE GAS LTDA</t>
         </is>
       </c>
       <c r="G243" t="n">
-        <v>807530.78</v>
+        <v>2011684.08</v>
       </c>
     </row>
     <row r="244">
@@ -7068,24 +6988,24 @@
         <v>2026</v>
       </c>
       <c r="B244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C244" t="n">
-        <v>717</v>
+        <v>799</v>
       </c>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr">
         <is>
-          <t>49691436000163</t>
+          <t>56246312000134</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>BARBOSA BARBOSA COMERCIO VAREJISTA DE AL</t>
+          <t>FORT FIT ACADEMIA LTDA</t>
         </is>
       </c>
       <c r="G244" t="n">
-        <v>24438.53</v>
+        <v>305.9</v>
       </c>
     </row>
     <row r="245">
@@ -7093,24 +7013,24 @@
         <v>2026</v>
       </c>
       <c r="B245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C245" t="n">
-        <v>720</v>
+        <v>805</v>
       </c>
       <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr">
         <is>
-          <t>32535490000389</t>
+          <t>46356513000130</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>SANTOS COMERCIO DE ALIMENTOS LTDA</t>
+          <t>T S SUPERMERCADO LTDA</t>
         </is>
       </c>
       <c r="G245" t="n">
-        <v>1172708.32</v>
+        <v>25597.15</v>
       </c>
     </row>
     <row r="246">
@@ -7118,24 +7038,24 @@
         <v>2026</v>
       </c>
       <c r="B246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C246" t="n">
-        <v>725</v>
+        <v>806</v>
       </c>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
-          <t>43623019000105</t>
+          <t>34073492000590</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>DARLAN C DO CARMO</t>
+          <t>GEOVANNE GOMES DOS SANTOS LTDA</t>
         </is>
       </c>
       <c r="G246" t="n">
-        <v>39988.5</v>
+        <v>13426.71</v>
       </c>
     </row>
     <row r="247">
@@ -7143,24 +7063,24 @@
         <v>2026</v>
       </c>
       <c r="B247" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C247" t="n">
-        <v>731</v>
+        <v>809</v>
       </c>
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>35229626000230</t>
+          <t>07664783000157</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>BARBOSA CARVALHO COMERCIO VAREJISTA DE P</t>
+          <t>DUVALE CONSTRUCAO LTDA</t>
         </is>
       </c>
       <c r="G247" t="n">
-        <v>356581.38</v>
+        <v>229448.48</v>
       </c>
     </row>
     <row r="248">
@@ -7168,24 +7088,24 @@
         <v>2026</v>
       </c>
       <c r="B248" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C248" t="n">
-        <v>734</v>
+        <v>810</v>
       </c>
       <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
-          <t>53930552000165</t>
+          <t>07664783000319</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>ALIANCA ATACADO LTDA</t>
+          <t>DUVALE CONSTRUCAO LTDA</t>
         </is>
       </c>
       <c r="G248" t="n">
-        <v>297536.38</v>
+        <v>203493.33</v>
       </c>
     </row>
     <row r="249">
@@ -7193,24 +7113,24 @@
         <v>2026</v>
       </c>
       <c r="B249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C249" t="n">
-        <v>745</v>
+        <v>811</v>
       </c>
       <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
-          <t>39270496000159</t>
+          <t>07664783000408</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>V B R COMERCIO DE FRUTAS LTDA</t>
+          <t>DUVALE CONSTRUCAO LTDA</t>
         </is>
       </c>
       <c r="G249" t="n">
-        <v>53647.06</v>
+        <v>19199.33</v>
       </c>
     </row>
     <row r="250">
@@ -7218,24 +7138,24 @@
         <v>2026</v>
       </c>
       <c r="B250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C250" t="n">
-        <v>750</v>
+        <v>812</v>
       </c>
       <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
-          <t>35824052000167</t>
+          <t>12553683000193</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>UP TELECOM E SERVICOS LTDA</t>
+          <t>COMERCIAL BOUTIQUE DAS CARNES LTDA</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>17114.43</v>
+        <v>1863064.36</v>
       </c>
     </row>
     <row r="251">
@@ -7243,24 +7163,24 @@
         <v>2026</v>
       </c>
       <c r="B251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C251" t="n">
-        <v>753</v>
+        <v>816</v>
       </c>
       <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
-          <t>59706743000124</t>
+          <t>55993256000139</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>LINS GENEROS ALIMENTICIOS LTDA</t>
+          <t>BOI PRIME DUVALE LTDA</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>687226.22</v>
+        <v>21061.94</v>
       </c>
     </row>
     <row r="252">
@@ -7268,24 +7188,24 @@
         <v>2026</v>
       </c>
       <c r="B252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C252" t="n">
-        <v>755</v>
+        <v>817</v>
       </c>
       <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr">
         <is>
-          <t>43663474000550</t>
+          <t>22858811000160</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>MELISSIA C HARDY LTDA</t>
+          <t>P I ALMEIDA VIEIRA ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>82563.77</v>
+        <v>1201820.05</v>
       </c>
     </row>
     <row r="253">
@@ -7293,24 +7213,24 @@
         <v>2026</v>
       </c>
       <c r="B253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C253" t="n">
-        <v>756</v>
+        <v>818</v>
       </c>
       <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
-          <t>48681098000116</t>
+          <t>61570926000107</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>SA RIBEIRO COMERCIO ALIMENTICIO LTDA</t>
+          <t>COMERCIAL CORTEZ LTDA</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>1311781.38</v>
+        <v>449430.74</v>
       </c>
     </row>
     <row r="254">
@@ -7318,24 +7238,24 @@
         <v>2026</v>
       </c>
       <c r="B254" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C254" t="n">
-        <v>757</v>
+        <v>829</v>
       </c>
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
-          <t>54460259000144</t>
+          <t>34021653000179</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>W K COSTA LEITE</t>
+          <t>J J M MERCADO E PADARIA LTDA</t>
         </is>
       </c>
       <c r="G254" t="n">
-        <v>1015947.43</v>
+        <v>336447.42</v>
       </c>
     </row>
     <row r="255">
@@ -7343,24 +7263,24 @@
         <v>2026</v>
       </c>
       <c r="B255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C255" t="n">
-        <v>758</v>
+        <v>830</v>
       </c>
       <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>59685839000153</t>
+          <t>63735051000181</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>CLINICA VIOTTO MACEIO LTDA</t>
+          <t>AMBROSIO SERVICOS LTDA</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>1861.44</v>
+        <v>15652.08</v>
       </c>
     </row>
     <row r="256">
@@ -7368,24 +7288,24 @@
         <v>2026</v>
       </c>
       <c r="B256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C256" t="n">
-        <v>759</v>
+        <v>836</v>
       </c>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
-          <t>59825964000111</t>
+          <t>35356543000120</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>PAIVA SANTOS LTDA</t>
+          <t>MARIA SELMA FLORIANO DE LIRA LTDA.</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>80031.53999999999</v>
+        <v>367087.44</v>
       </c>
     </row>
     <row r="257">
@@ -7393,24 +7313,24 @@
         <v>2026</v>
       </c>
       <c r="B257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C257" t="n">
-        <v>760</v>
+        <v>837</v>
       </c>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
-          <t>60126014000188</t>
+          <t>17257974000158</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>MAXX ATACAREJO COMERCIO DE ALIMENTOS LTD</t>
+          <t>C C G SANTOS COMERCIO</t>
         </is>
       </c>
       <c r="G257" t="n">
-        <v>98922.75</v>
+        <v>460.35</v>
       </c>
     </row>
     <row r="258">
@@ -7418,24 +7338,24 @@
         <v>2026</v>
       </c>
       <c r="B258" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C258" t="n">
-        <v>762</v>
+        <v>838</v>
       </c>
       <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr">
         <is>
-          <t>07536029000131</t>
+          <t>64255510000192</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>WILDSON XAVIER DA SILVA LTDA</t>
+          <t>DUVALE PISOS LTDA</t>
         </is>
       </c>
       <c r="G258" t="n">
-        <v>112616.01</v>
+        <v>66464.72</v>
       </c>
     </row>
     <row r="259">
@@ -7443,24 +7363,24 @@
         <v>2026</v>
       </c>
       <c r="B259" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C259" t="n">
-        <v>766</v>
+        <v>839</v>
       </c>
       <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
-          <t>22664506000480</t>
+          <t>05196097000173</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS GLOBO LTDA</t>
+          <t>C A LEMOS LTDA</t>
         </is>
       </c>
       <c r="G259" t="n">
-        <v>62441.24</v>
+        <v>79225.73</v>
       </c>
     </row>
     <row r="260">
@@ -7468,24 +7388,24 @@
         <v>2026</v>
       </c>
       <c r="B260" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C260" t="n">
-        <v>767</v>
+        <v>841</v>
       </c>
       <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr">
         <is>
-          <t>03339821001117</t>
+          <t>43069037000189</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>REVENDEDORA DE PNEUS TC LTDA.</t>
+          <t>EXPACER EDUCACAO EMPREENDEDORA LTDA</t>
         </is>
       </c>
       <c r="G260" t="n">
-        <v>97446.8</v>
+        <v>430068.13</v>
       </c>
     </row>
     <row r="261">
@@ -7493,24 +7413,24 @@
         <v>2026</v>
       </c>
       <c r="B261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C261" t="n">
-        <v>769</v>
+        <v>842</v>
       </c>
       <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
-          <t>03339821000900</t>
+          <t>34399712000147</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>REVENDEDORA DE PNEUS TC LTDA.</t>
+          <t>INOVAR SOLUCOES EDUCACIONAIS LTDA</t>
         </is>
       </c>
       <c r="G261" t="n">
-        <v>328348.02</v>
+        <v>411.9</v>
       </c>
     </row>
     <row r="262">
@@ -7518,24 +7438,24 @@
         <v>2026</v>
       </c>
       <c r="B262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C262" t="n">
-        <v>770</v>
+        <v>843</v>
       </c>
       <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
-          <t>03339821000145</t>
+          <t>51997114000199</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>REVENDEDORA DE PNEUS TC LTDA.</t>
+          <t>SUPERMERCADO BOA VISTA LTDA</t>
         </is>
       </c>
       <c r="G262" t="n">
-        <v>294085.47</v>
+        <v>1047035.64</v>
       </c>
     </row>
     <row r="263">
@@ -7543,24 +7463,24 @@
         <v>2026</v>
       </c>
       <c r="B263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C263" t="n">
-        <v>771</v>
+        <v>844</v>
       </c>
       <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
-          <t>03339821000226</t>
+          <t>05196097000254</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>REVENDEDORA DE PNEUS TC LTDA.</t>
+          <t>C A LEMOS LTDA</t>
         </is>
       </c>
       <c r="G263" t="n">
-        <v>802495.4</v>
+        <v>479086.58</v>
       </c>
     </row>
     <row r="264">
@@ -7568,24 +7488,24 @@
         <v>2026</v>
       </c>
       <c r="B264" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C264" t="n">
-        <v>772</v>
+        <v>852</v>
       </c>
       <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr">
         <is>
-          <t>03339821000307</t>
+          <t>05903763000166</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>REVENDEDORA DE PNEUS TC LTDA.</t>
+          <t>CORDEIRO LTDA</t>
         </is>
       </c>
       <c r="G264" t="n">
-        <v>809652.98</v>
+        <v>375957.76</v>
       </c>
     </row>
     <row r="265">
@@ -7593,24 +7513,24 @@
         <v>2026</v>
       </c>
       <c r="B265" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C265" t="n">
-        <v>773</v>
+        <v>854</v>
       </c>
       <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr">
         <is>
-          <t>03339821001036</t>
+          <t>37919357000188</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>REVENDEDORA DE PNEUS TC LTDA.</t>
+          <t>SUPERMERCADO VIA NORTE LTDA</t>
         </is>
       </c>
       <c r="G265" t="n">
-        <v>139086.89</v>
+        <v>275513.42</v>
       </c>
     </row>
     <row r="266">
@@ -7618,799 +7538,24 @@
         <v>2026</v>
       </c>
       <c r="B266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C266" t="n">
-        <v>774</v>
+        <v>855</v>
       </c>
       <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
-          <t>03339821000730</t>
+          <t>02226172000103</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>REVENDEDORA DE PNEUS TC LTDA.</t>
+          <t>MANOEL PEREIRA DE SOUZA MERCEARIA LTDA</t>
         </is>
       </c>
       <c r="G266" t="n">
-        <v>928517.55</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B267" t="n">
-        <v>1</v>
-      </c>
-      <c r="C267" t="n">
-        <v>775</v>
-      </c>
-      <c r="D267" t="inlineStr"/>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>03339821000811</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>REVENDEDORA DE PNEUS TC LTDA.</t>
-        </is>
-      </c>
-      <c r="G267" t="n">
-        <v>301702.16</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B268" t="n">
-        <v>1</v>
-      </c>
-      <c r="C268" t="n">
-        <v>783</v>
-      </c>
-      <c r="D268" t="inlineStr"/>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>52016958000174</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>SEVEN SUPERMERCADO LTDA</t>
-        </is>
-      </c>
-      <c r="G268" t="n">
-        <v>754126.4</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B269" t="n">
-        <v>1</v>
-      </c>
-      <c r="C269" t="n">
-        <v>784</v>
-      </c>
-      <c r="D269" t="inlineStr"/>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>52016387000178</t>
-        </is>
-      </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>SEVEN GAS LTDA</t>
-        </is>
-      </c>
-      <c r="G269" t="n">
-        <v>52869</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B270" t="n">
-        <v>1</v>
-      </c>
-      <c r="C270" t="n">
-        <v>785</v>
-      </c>
-      <c r="D270" t="inlineStr"/>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>61167515000175</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>LACERDA E BARBOSA LTDA</t>
-        </is>
-      </c>
-      <c r="G270" t="n">
-        <v>7528.79</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B271" t="n">
-        <v>1</v>
-      </c>
-      <c r="C271" t="n">
-        <v>796</v>
-      </c>
-      <c r="D271" t="inlineStr"/>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>60142273000100</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>CONSORCIO CEIS ARAPIRACA</t>
-        </is>
-      </c>
-      <c r="G271" t="n">
-        <v>709546.99</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B272" t="n">
-        <v>1</v>
-      </c>
-      <c r="C272" t="n">
-        <v>797</v>
-      </c>
-      <c r="D272" t="inlineStr"/>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>61520245000134</t>
-        </is>
-      </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>L L COMERCIO DE GAS LTDA</t>
-        </is>
-      </c>
-      <c r="G272" t="n">
-        <v>1919194.9</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B273" t="n">
-        <v>1</v>
-      </c>
-      <c r="C273" t="n">
-        <v>799</v>
-      </c>
-      <c r="D273" t="inlineStr"/>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>56246312000134</t>
-        </is>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>FORT FIT ACADEMIA LTDA</t>
-        </is>
-      </c>
-      <c r="G273" t="n">
-        <v>261.25</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B274" t="n">
-        <v>1</v>
-      </c>
-      <c r="C274" t="n">
-        <v>802</v>
-      </c>
-      <c r="D274" t="inlineStr"/>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>62122278000199</t>
-        </is>
-      </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>CONSORCIO LT01- CRECHES PE</t>
-        </is>
-      </c>
-      <c r="G274" t="n">
-        <v>958639.8100000001</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B275" t="n">
-        <v>1</v>
-      </c>
-      <c r="C275" t="n">
-        <v>804</v>
-      </c>
-      <c r="D275" t="inlineStr"/>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>31537528000128</t>
-        </is>
-      </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>RODRIGO MARQUES DE ARAUJO 70893337447</t>
-        </is>
-      </c>
-      <c r="G275" t="n">
-        <v>19796.9</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B276" t="n">
-        <v>1</v>
-      </c>
-      <c r="C276" t="n">
-        <v>805</v>
-      </c>
-      <c r="D276" t="inlineStr"/>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>46356513000130</t>
-        </is>
-      </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>T S SUPERMERCADO LTDA</t>
-        </is>
-      </c>
-      <c r="G276" t="n">
-        <v>19150.98</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B277" t="n">
-        <v>1</v>
-      </c>
-      <c r="C277" t="n">
-        <v>806</v>
-      </c>
-      <c r="D277" t="inlineStr"/>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>34073492000590</t>
-        </is>
-      </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>GEOVANNE GOMES DOS SANTOS LTDA</t>
-        </is>
-      </c>
-      <c r="G277" t="n">
-        <v>32776.55</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B278" t="n">
-        <v>1</v>
-      </c>
-      <c r="C278" t="n">
-        <v>809</v>
-      </c>
-      <c r="D278" t="inlineStr"/>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>07664783000157</t>
-        </is>
-      </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>DUVALE CONSTRUCAO LTDA</t>
-        </is>
-      </c>
-      <c r="G278" t="n">
-        <v>302135.01</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B279" t="n">
-        <v>1</v>
-      </c>
-      <c r="C279" t="n">
-        <v>812</v>
-      </c>
-      <c r="D279" t="inlineStr"/>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>12553683000193</t>
-        </is>
-      </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>COMERCIAL BOUTIQUE DAS CARNES LTDA</t>
-        </is>
-      </c>
-      <c r="G279" t="n">
-        <v>839702.8199999999</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B280" t="n">
-        <v>1</v>
-      </c>
-      <c r="C280" t="n">
-        <v>816</v>
-      </c>
-      <c r="D280" t="inlineStr"/>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>55993256000139</t>
-        </is>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>BOI PRIME DUVALE LTDA</t>
-        </is>
-      </c>
-      <c r="G280" t="n">
-        <v>12709.56</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B281" t="n">
-        <v>1</v>
-      </c>
-      <c r="C281" t="n">
-        <v>817</v>
-      </c>
-      <c r="D281" t="inlineStr"/>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>22858811000160</t>
-        </is>
-      </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>P I ALMEIDA VIEIRA ALIMENTOS LTDA</t>
-        </is>
-      </c>
-      <c r="G281" t="n">
-        <v>1473752.37</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B282" t="n">
-        <v>1</v>
-      </c>
-      <c r="C282" t="n">
-        <v>818</v>
-      </c>
-      <c r="D282" t="inlineStr"/>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>61570926000107</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>COMERCIAL CORTEZ LTDA</t>
-        </is>
-      </c>
-      <c r="G282" t="n">
-        <v>603579.17</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B283" t="n">
-        <v>1</v>
-      </c>
-      <c r="C283" t="n">
-        <v>819</v>
-      </c>
-      <c r="D283" t="inlineStr"/>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>59204103000116</t>
-        </is>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>MARDON WILLIAM ALVES LIMA LTDA</t>
-        </is>
-      </c>
-      <c r="G283" t="n">
-        <v>214265.61</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B284" t="n">
-        <v>1</v>
-      </c>
-      <c r="C284" t="n">
-        <v>825</v>
-      </c>
-      <c r="D284" t="inlineStr"/>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>63196074000165</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>M G A RESTAURANTE E LANCHONETE LTDA</t>
-        </is>
-      </c>
-      <c r="G284" t="n">
-        <v>103.79</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B285" t="n">
-        <v>1</v>
-      </c>
-      <c r="C285" t="n">
-        <v>828</v>
-      </c>
-      <c r="D285" t="inlineStr"/>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>63742096000183</t>
-        </is>
-      </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>GOMES SERVICOS EMPRESARIAIS LTDA</t>
-        </is>
-      </c>
-      <c r="G285" t="n">
-        <v>25497</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B286" t="n">
-        <v>1</v>
-      </c>
-      <c r="C286" t="n">
-        <v>829</v>
-      </c>
-      <c r="D286" t="inlineStr"/>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>34021653000179</t>
-        </is>
-      </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>J J M MERCADO E PADARIA LTDA</t>
-        </is>
-      </c>
-      <c r="G286" t="n">
-        <v>351613.21</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B287" t="n">
-        <v>1</v>
-      </c>
-      <c r="C287" t="n">
-        <v>836</v>
-      </c>
-      <c r="D287" t="inlineStr"/>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>35356543000120</t>
-        </is>
-      </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>MARIA SELMA FLORIANO DE LIRA LTDA.</t>
-        </is>
-      </c>
-      <c r="G287" t="n">
-        <v>437733.72</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B288" t="n">
-        <v>1</v>
-      </c>
-      <c r="C288" t="n">
-        <v>837</v>
-      </c>
-      <c r="D288" t="inlineStr"/>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>17257974000158</t>
-        </is>
-      </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>C C G SANTOS COMERCIO</t>
-        </is>
-      </c>
-      <c r="G288" t="n">
-        <v>15793.13</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B289" t="n">
-        <v>1</v>
-      </c>
-      <c r="C289" t="n">
-        <v>839</v>
-      </c>
-      <c r="D289" t="inlineStr"/>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>05196097000173</t>
-        </is>
-      </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>C A LEMOS LTDA</t>
-        </is>
-      </c>
-      <c r="G289" t="n">
-        <v>27390.56</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B290" t="n">
-        <v>1</v>
-      </c>
-      <c r="C290" t="n">
-        <v>841</v>
-      </c>
-      <c r="D290" t="inlineStr"/>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>43069037000189</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>EXPACER EDUCACAO EMPREENDEDORA LTDA</t>
-        </is>
-      </c>
-      <c r="G290" t="n">
-        <v>2780.88</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B291" t="n">
-        <v>1</v>
-      </c>
-      <c r="C291" t="n">
-        <v>842</v>
-      </c>
-      <c r="D291" t="inlineStr"/>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>34399712000147</t>
-        </is>
-      </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>INOVAR SOLUCOES EDUCACIONAIS LTDA</t>
-        </is>
-      </c>
-      <c r="G291" t="n">
-        <v>2486.5</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B292" t="n">
-        <v>1</v>
-      </c>
-      <c r="C292" t="n">
-        <v>843</v>
-      </c>
-      <c r="D292" t="inlineStr"/>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>51997114000199</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>SUPERMERCADO BOA VISTA LTDA</t>
-        </is>
-      </c>
-      <c r="G292" t="n">
-        <v>1184653.27</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B293" t="n">
-        <v>1</v>
-      </c>
-      <c r="C293" t="n">
-        <v>844</v>
-      </c>
-      <c r="D293" t="inlineStr"/>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>05196097000254</t>
-        </is>
-      </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>C A LEMOS LTDA</t>
-        </is>
-      </c>
-      <c r="G293" t="n">
-        <v>839253.88</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B294" t="n">
-        <v>1</v>
-      </c>
-      <c r="C294" t="n">
-        <v>849</v>
-      </c>
-      <c r="D294" t="inlineStr"/>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>40941565000198</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>FLOR DO SERTAO COMERCIO DE PRODUTOS AGRO</t>
-        </is>
-      </c>
-      <c r="G294" t="n">
-        <v>44565.62</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B295" t="n">
-        <v>1</v>
-      </c>
-      <c r="C295" t="n">
-        <v>852</v>
-      </c>
-      <c r="D295" t="inlineStr"/>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>05903763000166</t>
-        </is>
-      </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>CORDEIRO LTDA</t>
-        </is>
-      </c>
-      <c r="G295" t="n">
-        <v>19571.09</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B296" t="n">
-        <v>1</v>
-      </c>
-      <c r="C296" t="n">
-        <v>854</v>
-      </c>
-      <c r="D296" t="inlineStr"/>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>37919357000188</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>SUPERMERCADO VIA NORTE LTDA</t>
-        </is>
-      </c>
-      <c r="G296" t="n">
-        <v>284680.99</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B297" t="n">
-        <v>1</v>
-      </c>
-      <c r="C297" t="n">
-        <v>855</v>
-      </c>
-      <c r="D297" t="inlineStr"/>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>02226172000103</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>MANOEL PEREIRA DE SOUZA MERCEARIA LTDA</t>
-        </is>
-      </c>
-      <c r="G297" t="n">
-        <v>156418.27</v>
+        <v>106156.76</v>
       </c>
     </row>
   </sheetData>
